--- a/_Source - CollegeControlTotal - 2025-02-14_Start.xlsx
+++ b/_Source - CollegeControlTotal - 2025-02-14_Start.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Desktop_Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\TDM-INP-College-Enrollment\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E45F1F1-8399-4D09-8170-582139454AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="270" windowWidth="28800" windowHeight="14655" tabRatio="728" firstSheet="3" activeTab="9"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="728" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Export_ControlTot" sheetId="11" r:id="rId1"/>
@@ -29,7 +30,7 @@
     <sheet name="USHE 2020 Campus Totals" sheetId="3" r:id="rId15"/>
     <sheet name="MAG College Enrollment Forecast" sheetId="12" r:id="rId16"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="201">
   <si>
     <t>https://ushe.edu/institutional-data-resources-headcount/</t>
   </si>
@@ -612,9 +613,6 @@
     <t>Source: 2019 RTP</t>
   </si>
   <si>
-    <t>Source: USHE Enrollment data by Zip (Base Distribution Jupyter Notebook)</t>
-  </si>
-  <si>
     <t>Note:</t>
   </si>
   <si>
@@ -659,11 +657,38 @@
   <si>
     <t>*USHE not currently releasing updates forecasts</t>
   </si>
+  <si>
+    <t>Source: USHE Enrollment data by Zip (Base Distribution: 4-CollegeCampusDisaggregation.Rmd)</t>
+  </si>
+  <si>
+    <t>Old Data</t>
+  </si>
+  <si>
+    <t>Might have to fill this.</t>
+  </si>
+  <si>
+    <t>Need to update</t>
+  </si>
+  <si>
+    <t>Probably from College Survey</t>
+  </si>
+  <si>
+    <t>Not updated</t>
+  </si>
+  <si>
+    <t>This has to update to 2055</t>
+  </si>
+  <si>
+    <t>project until 2060</t>
+  </si>
+  <si>
+    <t>Project until 2060</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
@@ -989,7 +1014,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="2" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1236,9 +1261,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1249,16 +1271,11 @@
     <xf numFmtId="167" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="15" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1268,7 +1285,14 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="3" builtinId="3"/>
@@ -1297,7 +1321,7 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -1336,7 +1360,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1783,7 +1806,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-6C95-4AF9-9677-75D0BF8DBF4A}"/>
             </c:ext>
@@ -2200,7 +2223,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-6C95-4AF9-9677-75D0BF8DBF4A}"/>
             </c:ext>
@@ -2617,7 +2640,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-6C95-4AF9-9677-75D0BF8DBF4A}"/>
             </c:ext>
@@ -3034,7 +3057,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000003-6C95-4AF9-9677-75D0BF8DBF4A}"/>
             </c:ext>
@@ -3451,7 +3474,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000004-6C95-4AF9-9677-75D0BF8DBF4A}"/>
             </c:ext>
@@ -3868,7 +3891,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000005-6C95-4AF9-9677-75D0BF8DBF4A}"/>
             </c:ext>
@@ -4287,7 +4310,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000006-6C95-4AF9-9677-75D0BF8DBF4A}"/>
             </c:ext>
@@ -4706,7 +4729,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000007-6C95-4AF9-9677-75D0BF8DBF4A}"/>
             </c:ext>
@@ -5125,7 +5148,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000008-6C95-4AF9-9677-75D0BF8DBF4A}"/>
             </c:ext>
@@ -5544,7 +5567,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000009-6C95-4AF9-9677-75D0BF8DBF4A}"/>
             </c:ext>
@@ -5963,7 +5986,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{0000000A-6C95-4AF9-9677-75D0BF8DBF4A}"/>
             </c:ext>
@@ -6382,7 +6405,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{0000000B-6C95-4AF9-9677-75D0BF8DBF4A}"/>
             </c:ext>
@@ -6802,7 +6825,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{0000000C-6C95-4AF9-9677-75D0BF8DBF4A}"/>
             </c:ext>
@@ -7222,7 +7245,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{0000000D-6C95-4AF9-9677-75D0BF8DBF4A}"/>
             </c:ext>
@@ -7374,7 +7397,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -7407,7 +7429,7 @@
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
-    <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+    <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
           <c16r3:dispNaAsBlank val="1"/>
@@ -7449,7 +7471,7 @@
 </file>
 
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -7623,7 +7645,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-F488-4F6F-B8FC-239954948267}"/>
             </c:ext>
@@ -7751,7 +7773,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000005-F488-4F6F-B8FC-239954948267}"/>
             </c:ext>
@@ -7810,7 +7832,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000006-F488-4F6F-B8FC-239954948267}"/>
             </c:ext>
@@ -8037,7 +8059,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-9DD6-48A5-BA59-1EDEEA739F36}"/>
             </c:ext>
@@ -8200,7 +8222,6 @@
         <c:idx val="5"/>
         <c:delete val="1"/>
       </c:legendEntry>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -8233,7 +8254,7 @@
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
-    <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+    <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
           <c16r3:dispNaAsBlank val="1"/>
@@ -8275,7 +8296,7 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -8314,7 +8335,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -8761,7 +8781,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-7425-44AD-8193-F239116FDCF5}"/>
             </c:ext>
@@ -8914,7 +8934,7 @@
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="zero"/>
     <c:showDLblsOverMax val="0"/>
-    <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+    <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
           <c16r3:dispNaAsBlank val="1"/>
@@ -8956,7 +8976,7 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -8995,7 +9015,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -9262,7 +9281,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-54C9-4473-BE7D-5D3B04CD9771}"/>
             </c:ext>
@@ -9415,7 +9434,7 @@
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="zero"/>
     <c:showDLblsOverMax val="0"/>
-    <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+    <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
           <c16r3:dispNaAsBlank val="1"/>
@@ -9457,7 +9476,7 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -9736,7 +9755,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-1282-4053-85BF-D36622F55D0B}"/>
             </c:ext>
@@ -9840,7 +9859,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-1282-4053-85BF-D36622F55D0B}"/>
             </c:ext>
@@ -9968,7 +9987,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000005-1282-4053-85BF-D36622F55D0B}"/>
             </c:ext>
@@ -10027,7 +10046,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000004-1282-4053-85BF-D36622F55D0B}"/>
             </c:ext>
@@ -10212,7 +10231,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000003-5579-4878-B9E0-D9341EFE46CF}"/>
             </c:ext>
@@ -10378,7 +10397,6 @@
         <c:idx val="7"/>
         <c:delete val="1"/>
       </c:legendEntry>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -10411,7 +10429,7 @@
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
-    <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+    <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
           <c16r3:dispNaAsBlank val="1"/>
@@ -10453,7 +10471,7 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -10732,7 +10750,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-437D-441E-8CA1-A3C31C8FEFD5}"/>
             </c:ext>
@@ -10836,7 +10854,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000003-437D-441E-8CA1-A3C31C8FEFD5}"/>
             </c:ext>
@@ -10964,7 +10982,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000005-437D-441E-8CA1-A3C31C8FEFD5}"/>
             </c:ext>
@@ -11023,7 +11041,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000006-437D-441E-8CA1-A3C31C8FEFD5}"/>
             </c:ext>
@@ -11206,7 +11224,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000003-8291-4C9C-9FB1-308A80325282}"/>
             </c:ext>
@@ -11372,7 +11390,6 @@
         <c:idx val="7"/>
         <c:delete val="1"/>
       </c:legendEntry>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -11405,7 +11422,7 @@
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
-    <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+    <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
           <c16r3:dispNaAsBlank val="1"/>
@@ -11447,7 +11464,7 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -11726,7 +11743,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-262C-4D1B-BB8B-E4F7AB8B87B9}"/>
             </c:ext>
@@ -11830,7 +11847,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000003-262C-4D1B-BB8B-E4F7AB8B87B9}"/>
             </c:ext>
@@ -11958,7 +11975,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000005-262C-4D1B-BB8B-E4F7AB8B87B9}"/>
             </c:ext>
@@ -12017,7 +12034,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000006-262C-4D1B-BB8B-E4F7AB8B87B9}"/>
             </c:ext>
@@ -12069,7 +12086,7 @@
               </c:spPr>
             </c:marker>
             <c:bubble3D val="0"/>
-            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+            <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000004-7773-4901-91E0-F1EA12BDB5F6}"/>
               </c:ext>
@@ -12226,7 +12243,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000003-7773-4901-91E0-F1EA12BDB5F6}"/>
             </c:ext>
@@ -12391,7 +12408,6 @@
         <c:idx val="7"/>
         <c:delete val="1"/>
       </c:legendEntry>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -12424,7 +12440,7 @@
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
-    <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+    <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
           <c16r3:dispNaAsBlank val="1"/>
@@ -12466,7 +12482,7 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -12745,7 +12761,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-B831-4F91-A79F-255456EFB6C8}"/>
             </c:ext>
@@ -12849,7 +12865,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000003-B831-4F91-A79F-255456EFB6C8}"/>
             </c:ext>
@@ -12977,7 +12993,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000005-B831-4F91-A79F-255456EFB6C8}"/>
             </c:ext>
@@ -13029,7 +13045,7 @@
               </c:spPr>
             </c:marker>
             <c:bubble3D val="0"/>
-            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+            <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000003-94A6-487E-A6F0-693E2BB8A9D8}"/>
               </c:ext>
@@ -13060,7 +13076,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000006-B831-4F91-A79F-255456EFB6C8}"/>
             </c:ext>
@@ -13245,7 +13261,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000004-94A6-487E-A6F0-693E2BB8A9D8}"/>
             </c:ext>
@@ -13410,7 +13426,6 @@
         <c:idx val="7"/>
         <c:delete val="1"/>
       </c:legendEntry>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -13443,7 +13458,7 @@
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
-    <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+    <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
           <c16r3:dispNaAsBlank val="1"/>
@@ -13485,7 +13500,7 @@
 </file>
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -13800,7 +13815,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-3A74-4781-ACED-B1A98497F406}"/>
             </c:ext>
@@ -13928,7 +13943,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000005-3A74-4781-ACED-B1A98497F406}"/>
             </c:ext>
@@ -13987,7 +14002,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000006-3A74-4781-ACED-B1A98497F406}"/>
             </c:ext>
@@ -14172,7 +14187,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-C237-4535-B7C7-31175CD4A089}"/>
             </c:ext>
@@ -14334,7 +14349,6 @@
         <c:idx val="5"/>
         <c:delete val="1"/>
       </c:legendEntry>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -14367,7 +14381,7 @@
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
-    <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+    <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
           <c16r3:dispNaAsBlank val="1"/>
@@ -14409,7 +14423,7 @@
 </file>
 
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -14631,7 +14645,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-BC61-47BB-8BCF-8D1D611131B5}"/>
             </c:ext>
@@ -14759,7 +14773,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000007-BC61-47BB-8BCF-8D1D611131B5}"/>
             </c:ext>
@@ -14818,7 +14832,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000006-BC61-47BB-8BCF-8D1D611131B5}"/>
             </c:ext>
@@ -15057,7 +15071,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000003-330F-41CF-8E17-74E90AC63C64}"/>
             </c:ext>
@@ -15220,7 +15234,6 @@
         <c:idx val="5"/>
         <c:delete val="1"/>
       </c:legendEntry>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -15253,7 +15266,7 @@
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
-    <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+    <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
           <c16r3:dispNaAsBlank val="1"/>
@@ -20861,7 +20874,7 @@
         <xdr:cNvPr id="5" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C758BB74-C52F-4EAC-94E7-B3D4F20B9207}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C758BB74-C52F-4EAC-94E7-B3D4F20B9207}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -20899,7 +20912,7 @@
         <xdr:cNvPr id="6" name="Chart 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C94BF622-72F0-4EFA-BC03-32D40E0BBD94}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C94BF622-72F0-4EFA-BC03-32D40E0BBD94}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -20937,7 +20950,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3BBA52D3-63EA-4037-953A-D61CA982A75E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3BBA52D3-63EA-4037-953A-D61CA982A75E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -20980,7 +20993,7 @@
         <xdr:cNvPr id="22" name="Chart 21">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{91CBB898-A0E3-4288-BDC2-BBC243FF9881}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91CBB898-A0E3-4288-BDC2-BBC243FF9881}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21018,7 +21031,7 @@
         <xdr:cNvPr id="23" name="Chart 22">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{986BAAD4-A38A-44BC-9BB3-A50EF5713D36}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{986BAAD4-A38A-44BC-9BB3-A50EF5713D36}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21056,7 +21069,7 @@
         <xdr:cNvPr id="24" name="Chart 23">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C722CC9E-91F6-4CCE-B1CA-D400ED437365}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C722CC9E-91F6-4CCE-B1CA-D400ED437365}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21094,7 +21107,7 @@
         <xdr:cNvPr id="25" name="Chart 24">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E654136D-6A0F-48C7-956E-AB3F5802EF67}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E654136D-6A0F-48C7-956E-AB3F5802EF67}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21132,7 +21145,7 @@
         <xdr:cNvPr id="26" name="Chart 25">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4A8DC08F-17BB-4ABD-BD3A-683405BC91AE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A8DC08F-17BB-4ABD-BD3A-683405BC91AE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21170,7 +21183,7 @@
         <xdr:cNvPr id="27" name="Chart 26">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{EDD82B92-0E97-430E-B1C0-7360767BC560}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EDD82B92-0E97-430E-B1C0-7360767BC560}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21208,7 +21221,7 @@
         <xdr:cNvPr id="28" name="Chart 27">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{BD3D5500-528B-4495-824B-EA310EF9350E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD3D5500-528B-4495-824B-EA310EF9350E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21251,7 +21264,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{47530349-986F-478B-A6D0-1E72A1F89A82}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47530349-986F-478B-A6D0-1E72A1F89A82}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21300,7 +21313,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4531E8D3-0968-B75F-63E7-FF06CB98CD51}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4531E8D3-0968-B75F-63E7-FF06CB98CD51}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21344,7 +21357,7 @@
         <xdr:cNvPr id="5" name="Picture 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8FA0C9D7-0378-F096-6D5D-527CEC9544E7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8FA0C9D7-0378-F096-6D5D-527CEC9544E7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21393,7 +21406,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0781F624-165D-C4E0-0E48-2671E8E54B1B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0781F624-165D-C4E0-0E48-2671E8E54B1B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21437,7 +21450,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5A6F2C61-FDAA-4F11-AF09-896FF347EA9E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A6F2C61-FDAA-4F11-AF09-896FF347EA9E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21481,7 +21494,7 @@
         <xdr:cNvPr id="4" name="Picture 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A88477F1-82C0-4588-9DC9-0A2ACFCF53A5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A88477F1-82C0-4588-9DC9-0A2ACFCF53A5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21522,7 +21535,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4"/>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0B00-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -21568,7 +21587,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{1669A7C5-91D1-386D-B34B-63981ED3867C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1669A7C5-91D1-386D-B34B-63981ED3867C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21612,7 +21631,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C8870E41-0605-E35C-E6EA-37BDB88F8961}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C8870E41-0605-E35C-E6EA-37BDB88F8961}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21656,7 +21675,7 @@
         <xdr:cNvPr id="6" name="Picture 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{98490862-385D-1115-23E8-5ED696D2B097}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98490862-385D-1115-23E8-5ED696D2B097}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21700,7 +21719,7 @@
         <xdr:cNvPr id="7" name="Picture 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{34C79F7D-5658-8BC3-7BC4-72F2AA87B54A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34C79F7D-5658-8BC3-7BC4-72F2AA87B54A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21744,7 +21763,7 @@
         <xdr:cNvPr id="8" name="Picture 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{FF116E29-9E89-1CF2-8D49-C419987E21F5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF116E29-9E89-1CF2-8D49-C419987E21F5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21788,7 +21807,7 @@
         <xdr:cNvPr id="9" name="Picture 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00A210A5-1DBD-D610-610B-69C854F5301C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00A210A5-1DBD-D610-610B-69C854F5301C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21829,7 +21848,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4"/>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0C00-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -21867,7 +21892,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 9"/>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0C00-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -21905,7 +21936,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Picture 10"/>
+        <xdr:cNvPr id="11" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0C00-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -21943,7 +21980,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Picture 11"/>
+        <xdr:cNvPr id="12" name="Picture 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0C00-00000C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -22265,11 +22308,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:U62"/>
+  <dimension ref="A1:U73"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="15" width="12.140625" style="7" customWidth="1"/>
@@ -26045,6 +26088,62 @@
         <v>3000</v>
       </c>
     </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A63" s="7">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A64" s="7">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="7">
+        <v>2053</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="7">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="7">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="7">
+        <v>2056</v>
+      </c>
+      <c r="B68" s="108"/>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="7">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="7">
+        <v>2058</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="7">
+        <v>2059</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="7">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="109" t="s">
+        <v>198</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -26052,7 +26151,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr>
     <tabColor theme="0" tint="-0.499984740745262"/>
   </sheetPr>
@@ -26078,30 +26177,30 @@
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
       <c r="J2" s="5"/>
-      <c r="Q2" s="105" t="s">
+      <c r="Q2" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="R2" s="106"/>
-      <c r="S2" s="106"/>
-      <c r="T2" s="106"/>
-      <c r="U2" s="105" t="s">
+      <c r="R2" s="104"/>
+      <c r="S2" s="104"/>
+      <c r="T2" s="104"/>
+      <c r="U2" s="103" t="s">
         <v>2</v>
       </c>
-      <c r="V2" s="106"/>
-      <c r="W2" s="106"/>
-      <c r="X2" s="106"/>
-      <c r="Y2" s="105" t="s">
+      <c r="V2" s="104"/>
+      <c r="W2" s="104"/>
+      <c r="X2" s="104"/>
+      <c r="Y2" s="103" t="s">
         <v>3</v>
       </c>
-      <c r="Z2" s="106"/>
-      <c r="AA2" s="106"/>
-      <c r="AB2" s="106"/>
-      <c r="AC2" s="105" t="s">
+      <c r="Z2" s="104"/>
+      <c r="AA2" s="104"/>
+      <c r="AB2" s="104"/>
+      <c r="AC2" s="103" t="s">
         <v>4</v>
       </c>
-      <c r="AD2" s="106"/>
-      <c r="AE2" s="106"/>
-      <c r="AF2" s="106"/>
+      <c r="AD2" s="104"/>
+      <c r="AE2" s="104"/>
+      <c r="AF2" s="104"/>
     </row>
     <row r="3" spans="1:32" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -26757,12 +26856,12 @@
       <c r="AC10" s="43">
         <v>5812</v>
       </c>
-      <c r="AD10" s="104"/>
-      <c r="AE10" s="104"/>
-      <c r="AF10" s="104"/>
+      <c r="AD10" s="44"/>
+      <c r="AE10" s="44"/>
+      <c r="AF10" s="44"/>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A11" s="96">
+      <c r="A11" s="3">
         <v>2023</v>
       </c>
       <c r="B11" s="18">
@@ -26786,7 +26885,7 @@
       <c r="H11" s="18">
         <v>6369</v>
       </c>
-      <c r="J11" s="96">
+      <c r="J11" s="3">
         <v>2023</v>
       </c>
       <c r="K11" s="26">
@@ -26805,7 +26904,7 @@
         <f t="shared" si="3"/>
         <v>5949</v>
       </c>
-      <c r="P11" s="103">
+      <c r="P11" s="101">
         <v>2023</v>
       </c>
       <c r="Q11" s="43">
@@ -26845,12 +26944,12 @@
       <c r="AC11" s="43">
         <v>5949</v>
       </c>
-      <c r="AD11" s="104"/>
-      <c r="AE11" s="104"/>
-      <c r="AF11" s="104"/>
+      <c r="AD11" s="44"/>
+      <c r="AE11" s="44"/>
+      <c r="AF11" s="44"/>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A12" s="96">
+      <c r="A12" s="3">
         <v>2024</v>
       </c>
       <c r="B12" s="18">
@@ -26865,7 +26964,7 @@
       <c r="E12" s="18">
         <v>27437</v>
       </c>
-      <c r="J12" s="96">
+      <c r="J12" s="3">
         <v>2024</v>
       </c>
       <c r="K12" s="26">
@@ -26884,7 +26983,7 @@
         <f t="shared" si="3"/>
         <v>6142</v>
       </c>
-      <c r="P12" s="103">
+      <c r="P12" s="101">
         <v>2024</v>
       </c>
       <c r="Q12" s="43">
@@ -26924,9 +27023,14 @@
       <c r="AC12" s="43">
         <v>6142</v>
       </c>
-      <c r="AD12" s="104"/>
-      <c r="AE12" s="104"/>
-      <c r="AF12" s="104"/>
+      <c r="AD12" s="44"/>
+      <c r="AE12" s="44"/>
+      <c r="AF12" s="44"/>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="F13" s="42" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
@@ -26966,11 +27070,11 @@
     <mergeCell ref="AC2:AF2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B19" r:id="rId1"/>
-    <hyperlink ref="B18" r:id="rId2"/>
-    <hyperlink ref="P19" r:id="rId3"/>
-    <hyperlink ref="B17" r:id="rId4"/>
-    <hyperlink ref="B16" r:id="rId5"/>
+    <hyperlink ref="B19" r:id="rId1" xr:uid="{00000000-0004-0000-0900-000000000000}"/>
+    <hyperlink ref="B18" r:id="rId2" xr:uid="{00000000-0004-0000-0900-000001000000}"/>
+    <hyperlink ref="P19" r:id="rId3" xr:uid="{00000000-0004-0000-0900-000002000000}"/>
+    <hyperlink ref="B17" r:id="rId4" xr:uid="{00000000-0004-0000-0900-000003000000}"/>
+    <hyperlink ref="B16" r:id="rId5" xr:uid="{00000000-0004-0000-0900-000004000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="0" r:id="rId6"/>
@@ -26979,7 +27083,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr>
     <tabColor theme="0" tint="-0.499984740745262"/>
   </sheetPr>
@@ -27030,13 +27134,13 @@
         <v>81</v>
       </c>
       <c r="L1" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="M1" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="M1" s="16" t="s">
+      <c r="N1" s="16" t="s">
         <v>182</v>
-      </c>
-      <c r="N1" s="16" t="s">
-        <v>183</v>
       </c>
       <c r="O1" s="16" t="s">
         <v>80</v>
@@ -27066,13 +27170,13 @@
         <v>72</v>
       </c>
       <c r="X1" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="Y1" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="Y1" s="16" t="s">
+      <c r="Z1" s="16" t="s">
         <v>187</v>
-      </c>
-      <c r="Z1" s="16" t="s">
-        <v>188</v>
       </c>
       <c r="AA1" s="16" t="s">
         <v>71</v>
@@ -27102,13 +27206,13 @@
         <v>63</v>
       </c>
       <c r="AJ1" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="AK1" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="AK1" s="16" t="s">
+      <c r="AL1" s="16" t="s">
         <v>190</v>
-      </c>
-      <c r="AL1" s="16" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="2" spans="1:38" x14ac:dyDescent="0.25">
@@ -27448,15 +27552,15 @@
     </row>
     <row r="8" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>185</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B8" r:id="rId1" location="enrollment"/>
+    <hyperlink ref="B8" r:id="rId1" location="enrollment" xr:uid="{00000000-0004-0000-0A00-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="0" r:id="rId2"/>
@@ -27464,7 +27568,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr>
     <tabColor theme="0" tint="-0.499984740745262"/>
   </sheetPr>
@@ -27529,7 +27633,7 @@
       <c r="N3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="V3" s="102">
+      <c r="V3" s="100">
         <v>45702</v>
       </c>
     </row>
@@ -27772,7 +27876,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="96">
+      <c r="A18" s="3">
         <v>2022</v>
       </c>
       <c r="B18" s="33">
@@ -27786,7 +27890,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="96">
+      <c r="A19" s="3">
         <v>2023</v>
       </c>
       <c r="B19" s="33">
@@ -27800,7 +27904,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="96">
+      <c r="A20" s="3">
         <v>2024</v>
       </c>
       <c r="B20" s="33">
@@ -27815,8 +27919,8 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1"/>
-    <hyperlink ref="N3" r:id="rId2"/>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{00000000-0004-0000-0B00-000000000000}"/>
+    <hyperlink ref="N3" r:id="rId2" xr:uid="{00000000-0004-0000-0B00-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId3"/>
@@ -27825,7 +27929,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr>
     <tabColor theme="0" tint="-0.499984740745262"/>
   </sheetPr>
@@ -27896,6 +28000,15 @@
         <v>1929</v>
       </c>
     </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>2020</v>
+      </c>
+      <c r="B8" s="106">
+        <f>AVERAGE(B7,B9)</f>
+        <v>1830</v>
+      </c>
+    </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="41">
         <v>2021</v>
@@ -27930,7 +28043,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D1" r:id="rId1"/>
+    <hyperlink ref="D1" r:id="rId1" xr:uid="{00000000-0004-0000-0C00-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId2"/>
@@ -27938,7 +28051,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <sheetPr>
     <tabColor theme="0" tint="-0.499984740745262"/>
   </sheetPr>
@@ -29404,7 +29517,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <sheetPr>
     <tabColor theme="0" tint="-0.499984740745262"/>
   </sheetPr>
@@ -29436,7 +29549,7 @@
         <v>50</v>
       </c>
       <c r="F1" s="95" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -29454,6 +29567,9 @@
       <c r="E2" s="12">
         <v>6</v>
       </c>
+      <c r="F2" s="42" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="3" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A3" s="40" t="s">
@@ -29888,196 +30004,196 @@
       </c>
     </row>
     <row r="31" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="107" t="s">
+      <c r="B31" s="105" t="s">
         <v>46</v>
       </c>
-      <c r="C31" s="107"/>
-      <c r="D31" s="107"/>
-      <c r="E31" s="107"/>
+      <c r="C31" s="105"/>
+      <c r="D31" s="105"/>
+      <c r="E31" s="105"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B32" s="107"/>
-      <c r="C32" s="107"/>
-      <c r="D32" s="107"/>
-      <c r="E32" s="107"/>
+      <c r="B32" s="105"/>
+      <c r="C32" s="105"/>
+      <c r="D32" s="105"/>
+      <c r="E32" s="105"/>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B33" s="107"/>
-      <c r="C33" s="107"/>
-      <c r="D33" s="107"/>
-      <c r="E33" s="107"/>
+      <c r="B33" s="105"/>
+      <c r="C33" s="105"/>
+      <c r="D33" s="105"/>
+      <c r="E33" s="105"/>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B34" s="107"/>
-      <c r="C34" s="107"/>
-      <c r="D34" s="107"/>
-      <c r="E34" s="107"/>
+      <c r="B34" s="105"/>
+      <c r="C34" s="105"/>
+      <c r="D34" s="105"/>
+      <c r="E34" s="105"/>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B35" s="107"/>
-      <c r="C35" s="107"/>
-      <c r="D35" s="107"/>
-      <c r="E35" s="107"/>
+      <c r="B35" s="105"/>
+      <c r="C35" s="105"/>
+      <c r="D35" s="105"/>
+      <c r="E35" s="105"/>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B36" s="107"/>
-      <c r="C36" s="107"/>
-      <c r="D36" s="107"/>
-      <c r="E36" s="107"/>
+      <c r="B36" s="105"/>
+      <c r="C36" s="105"/>
+      <c r="D36" s="105"/>
+      <c r="E36" s="105"/>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B37" s="107"/>
-      <c r="C37" s="107"/>
-      <c r="D37" s="107"/>
-      <c r="E37" s="107"/>
+      <c r="B37" s="105"/>
+      <c r="C37" s="105"/>
+      <c r="D37" s="105"/>
+      <c r="E37" s="105"/>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B38" s="107"/>
-      <c r="C38" s="107"/>
-      <c r="D38" s="107"/>
-      <c r="E38" s="107"/>
+      <c r="B38" s="105"/>
+      <c r="C38" s="105"/>
+      <c r="D38" s="105"/>
+      <c r="E38" s="105"/>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B39" s="107"/>
-      <c r="C39" s="107"/>
-      <c r="D39" s="107"/>
-      <c r="E39" s="107"/>
+      <c r="B39" s="105"/>
+      <c r="C39" s="105"/>
+      <c r="D39" s="105"/>
+      <c r="E39" s="105"/>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B40" s="107"/>
-      <c r="C40" s="107"/>
-      <c r="D40" s="107"/>
-      <c r="E40" s="107"/>
+      <c r="B40" s="105"/>
+      <c r="C40" s="105"/>
+      <c r="D40" s="105"/>
+      <c r="E40" s="105"/>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B41" s="107"/>
-      <c r="C41" s="107"/>
-      <c r="D41" s="107"/>
-      <c r="E41" s="107"/>
+      <c r="B41" s="105"/>
+      <c r="C41" s="105"/>
+      <c r="D41" s="105"/>
+      <c r="E41" s="105"/>
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B42" s="107"/>
-      <c r="C42" s="107"/>
-      <c r="D42" s="107"/>
-      <c r="E42" s="107"/>
+      <c r="B42" s="105"/>
+      <c r="C42" s="105"/>
+      <c r="D42" s="105"/>
+      <c r="E42" s="105"/>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B43" s="107"/>
-      <c r="C43" s="107"/>
-      <c r="D43" s="107"/>
-      <c r="E43" s="107"/>
+      <c r="B43" s="105"/>
+      <c r="C43" s="105"/>
+      <c r="D43" s="105"/>
+      <c r="E43" s="105"/>
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B44" s="107"/>
-      <c r="C44" s="107"/>
-      <c r="D44" s="107"/>
-      <c r="E44" s="107"/>
+      <c r="B44" s="105"/>
+      <c r="C44" s="105"/>
+      <c r="D44" s="105"/>
+      <c r="E44" s="105"/>
     </row>
     <row r="46" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B46" s="107" t="s">
+      <c r="B46" s="105" t="s">
         <v>44</v>
       </c>
-      <c r="C46" s="107"/>
-      <c r="D46" s="107"/>
-      <c r="E46" s="107"/>
+      <c r="C46" s="105"/>
+      <c r="D46" s="105"/>
+      <c r="E46" s="105"/>
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B47" s="107" t="s">
+      <c r="B47" s="105" t="s">
         <v>45</v>
       </c>
-      <c r="C47" s="107"/>
-      <c r="D47" s="107"/>
-      <c r="E47" s="107"/>
+      <c r="C47" s="105"/>
+      <c r="D47" s="105"/>
+      <c r="E47" s="105"/>
     </row>
     <row r="48" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B48" s="107"/>
-      <c r="C48" s="107"/>
-      <c r="D48" s="107"/>
-      <c r="E48" s="107"/>
+      <c r="B48" s="105"/>
+      <c r="C48" s="105"/>
+      <c r="D48" s="105"/>
+      <c r="E48" s="105"/>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B49" s="107"/>
-      <c r="C49" s="107"/>
-      <c r="D49" s="107"/>
-      <c r="E49" s="107"/>
+      <c r="B49" s="105"/>
+      <c r="C49" s="105"/>
+      <c r="D49" s="105"/>
+      <c r="E49" s="105"/>
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B50" s="107"/>
-      <c r="C50" s="107"/>
-      <c r="D50" s="107"/>
-      <c r="E50" s="107"/>
+      <c r="B50" s="105"/>
+      <c r="C50" s="105"/>
+      <c r="D50" s="105"/>
+      <c r="E50" s="105"/>
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B51" s="107"/>
-      <c r="C51" s="107"/>
-      <c r="D51" s="107"/>
-      <c r="E51" s="107"/>
+      <c r="B51" s="105"/>
+      <c r="C51" s="105"/>
+      <c r="D51" s="105"/>
+      <c r="E51" s="105"/>
     </row>
     <row r="52" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B52" s="107"/>
-      <c r="C52" s="107"/>
-      <c r="D52" s="107"/>
-      <c r="E52" s="107"/>
+      <c r="B52" s="105"/>
+      <c r="C52" s="105"/>
+      <c r="D52" s="105"/>
+      <c r="E52" s="105"/>
     </row>
     <row r="53" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B53" s="107"/>
-      <c r="C53" s="107"/>
-      <c r="D53" s="107"/>
-      <c r="E53" s="107"/>
+      <c r="B53" s="105"/>
+      <c r="C53" s="105"/>
+      <c r="D53" s="105"/>
+      <c r="E53" s="105"/>
     </row>
     <row r="54" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B54" s="107"/>
-      <c r="C54" s="107"/>
-      <c r="D54" s="107"/>
-      <c r="E54" s="107"/>
+      <c r="B54" s="105"/>
+      <c r="C54" s="105"/>
+      <c r="D54" s="105"/>
+      <c r="E54" s="105"/>
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B55" s="107"/>
-      <c r="C55" s="107"/>
-      <c r="D55" s="107"/>
-      <c r="E55" s="107"/>
+      <c r="B55" s="105"/>
+      <c r="C55" s="105"/>
+      <c r="D55" s="105"/>
+      <c r="E55" s="105"/>
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B56" s="107"/>
-      <c r="C56" s="107"/>
-      <c r="D56" s="107"/>
-      <c r="E56" s="107"/>
+      <c r="B56" s="105"/>
+      <c r="C56" s="105"/>
+      <c r="D56" s="105"/>
+      <c r="E56" s="105"/>
     </row>
     <row r="57" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B57" s="107"/>
-      <c r="C57" s="107"/>
-      <c r="D57" s="107"/>
-      <c r="E57" s="107"/>
+      <c r="B57" s="105"/>
+      <c r="C57" s="105"/>
+      <c r="D57" s="105"/>
+      <c r="E57" s="105"/>
     </row>
     <row r="58" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B58" s="107"/>
-      <c r="C58" s="107"/>
-      <c r="D58" s="107"/>
-      <c r="E58" s="107"/>
+      <c r="B58" s="105"/>
+      <c r="C58" s="105"/>
+      <c r="D58" s="105"/>
+      <c r="E58" s="105"/>
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B59" s="107"/>
-      <c r="C59" s="107"/>
-      <c r="D59" s="107"/>
-      <c r="E59" s="107"/>
+      <c r="B59" s="105"/>
+      <c r="C59" s="105"/>
+      <c r="D59" s="105"/>
+      <c r="E59" s="105"/>
     </row>
     <row r="60" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B60" s="107"/>
-      <c r="C60" s="107"/>
-      <c r="D60" s="107"/>
-      <c r="E60" s="107"/>
+      <c r="B60" s="105"/>
+      <c r="C60" s="105"/>
+      <c r="D60" s="105"/>
+      <c r="E60" s="105"/>
     </row>
     <row r="61" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B61" s="107"/>
-      <c r="C61" s="107"/>
-      <c r="D61" s="107"/>
-      <c r="E61" s="107"/>
+      <c r="B61" s="105"/>
+      <c r="C61" s="105"/>
+      <c r="D61" s="105"/>
+      <c r="E61" s="105"/>
     </row>
     <row r="62" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B62" s="107"/>
-      <c r="C62" s="107"/>
-      <c r="D62" s="107"/>
-      <c r="E62" s="107"/>
+      <c r="B62" s="105"/>
+      <c r="C62" s="105"/>
+      <c r="D62" s="105"/>
+      <c r="E62" s="105"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -30089,7 +30205,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <sheetPr>
     <tabColor theme="0" tint="-0.499984740745262"/>
   </sheetPr>
@@ -31764,7 +31880,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
@@ -31778,43 +31894,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="96" t="s">
         <v>175</v>
       </c>
-      <c r="B1" s="97" t="s">
+      <c r="B1" s="96" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="97" t="s">
+      <c r="C1" s="96" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="97" t="s">
+      <c r="D1" s="96" t="s">
         <v>100</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="F1" s="97" t="s">
+      <c r="F1" s="96" t="s">
         <v>107</v>
       </c>
-      <c r="G1" s="97" t="s">
+      <c r="G1" s="96" t="s">
         <v>106</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="I1" s="97" t="s">
+      <c r="I1" s="96" t="s">
         <v>52</v>
       </c>
-      <c r="J1" s="97" t="s">
+      <c r="J1" s="96" t="s">
         <v>55</v>
       </c>
-      <c r="K1" s="97" t="s">
+      <c r="K1" s="96" t="s">
         <v>53</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="M1" s="97" t="s">
+      <c r="M1" s="96" t="s">
         <v>54</v>
       </c>
       <c r="N1" s="3" t="s">
@@ -31832,22 +31948,22 @@
       <c r="R1" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="S1" s="97" t="s">
+      <c r="S1" s="96" t="s">
         <v>15</v>
       </c>
-      <c r="T1" s="97" t="s">
+      <c r="T1" s="96" t="s">
         <v>101</v>
       </c>
       <c r="U1" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="V1" s="97" t="s">
+      <c r="V1" s="96" t="s">
         <v>121</v>
       </c>
-      <c r="W1" s="97" t="s">
+      <c r="W1" s="96" t="s">
         <v>123</v>
       </c>
-      <c r="X1" s="97" t="s">
+      <c r="X1" s="96" t="s">
         <v>122</v>
       </c>
       <c r="Y1" s="3" t="s">
@@ -31870,7 +31986,7 @@
         <f>VLOOKUP(D1,'calc%concurrent'!$A$2:$B$15,2,FALSE)</f>
         <v>2.6040514489776623E-2</v>
       </c>
-      <c r="E2" s="100">
+      <c r="E2" s="99">
         <f>D2</f>
         <v>2.6040514489776623E-2</v>
       </c>
@@ -31882,7 +31998,7 @@
         <f>VLOOKUP(G1,'calc%concurrent'!$A$2:$B$15,2,FALSE)</f>
         <v>0.30851477449455678</v>
       </c>
-      <c r="H2" s="100">
+      <c r="H2" s="99">
         <f>G2</f>
         <v>0.30851477449455678</v>
       </c>
@@ -31898,7 +32014,7 @@
         <f>VLOOKUP(K1,'calc%concurrent'!$A$2:$B$15,2,FALSE)</f>
         <v>0.34092450566077115</v>
       </c>
-      <c r="L2" s="100">
+      <c r="L2" s="99">
         <f>K2</f>
         <v>0.34092450566077115</v>
       </c>
@@ -31906,23 +32022,23 @@
         <f>VLOOKUP(M1,'calc%concurrent'!$A$2:$B$15,2,FALSE)</f>
         <v>0.34092450566077115</v>
       </c>
-      <c r="N2" s="100">
+      <c r="N2" s="99">
         <f t="shared" ref="N2:R4" si="0">M2</f>
         <v>0.34092450566077115</v>
       </c>
-      <c r="O2" s="100">
+      <c r="O2" s="99">
         <f t="shared" si="0"/>
         <v>0.34092450566077115</v>
       </c>
-      <c r="P2" s="100">
+      <c r="P2" s="99">
         <f t="shared" si="0"/>
         <v>0.34092450566077115</v>
       </c>
-      <c r="Q2" s="100">
+      <c r="Q2" s="99">
         <f t="shared" si="0"/>
         <v>0.34092450566077115</v>
       </c>
-      <c r="R2" s="100">
+      <c r="R2" s="99">
         <f t="shared" si="0"/>
         <v>0.34092450566077115</v>
       </c>
@@ -31934,7 +32050,7 @@
         <f>VLOOKUP(T1,'calc%concurrent'!$A$2:$B$15,2,FALSE)</f>
         <v>0.26992028734364659</v>
       </c>
-      <c r="U2" s="100">
+      <c r="U2" s="99">
         <f>T2</f>
         <v>0.26992028734364659</v>
       </c>
@@ -31970,7 +32086,7 @@
         <f>VLOOKUP(D$1,'FTE Rate Calcs'!$A$2:$B$15,2,FALSE)</f>
         <v>1.0252202452927968</v>
       </c>
-      <c r="E3" s="100">
+      <c r="E3" s="99">
         <f t="shared" ref="E3:E4" si="1">D3</f>
         <v>1.0252202452927968</v>
       </c>
@@ -31982,7 +32098,7 @@
         <f>VLOOKUP(G$1,'FTE Rate Calcs'!$A$2:$B$15,2,FALSE)</f>
         <v>1.0375684282085227</v>
       </c>
-      <c r="H3" s="100">
+      <c r="H3" s="99">
         <f t="shared" ref="H3:H4" si="2">G3</f>
         <v>1.0375684282085227</v>
       </c>
@@ -31998,7 +32114,7 @@
         <f>VLOOKUP(K$1,'FTE Rate Calcs'!$A$2:$B$15,2,FALSE)</f>
         <v>1.2081372400182178</v>
       </c>
-      <c r="L3" s="100">
+      <c r="L3" s="99">
         <f t="shared" ref="L3:L4" si="3">K3</f>
         <v>1.2081372400182178</v>
       </c>
@@ -32006,23 +32122,23 @@
         <f>VLOOKUP(M$1,'FTE Rate Calcs'!$A$2:$B$15,2,FALSE)</f>
         <v>1.2081372400182178</v>
       </c>
-      <c r="N3" s="100">
+      <c r="N3" s="99">
         <f t="shared" si="0"/>
         <v>1.2081372400182178</v>
       </c>
-      <c r="O3" s="100">
+      <c r="O3" s="99">
         <f t="shared" si="0"/>
         <v>1.2081372400182178</v>
       </c>
-      <c r="P3" s="100">
+      <c r="P3" s="99">
         <f t="shared" si="0"/>
         <v>1.2081372400182178</v>
       </c>
-      <c r="Q3" s="100">
+      <c r="Q3" s="99">
         <f t="shared" si="0"/>
         <v>1.2081372400182178</v>
       </c>
-      <c r="R3" s="100">
+      <c r="R3" s="99">
         <f t="shared" si="0"/>
         <v>1.2081372400182178</v>
       </c>
@@ -32034,7 +32150,7 @@
         <f>VLOOKUP(T$1,'FTE Rate Calcs'!$A$2:$B$15,2,FALSE)</f>
         <v>1.0967771874057404</v>
       </c>
-      <c r="U3" s="100">
+      <c r="U3" s="99">
         <f t="shared" ref="U3:U4" si="4">T3</f>
         <v>1.0967771874057404</v>
       </c>
@@ -32070,7 +32186,7 @@
         <f>VLOOKUP(D$1,'HBC Rates'!$A$2:$B$15,2,FALSE)</f>
         <v>0.93010000000000004</v>
       </c>
-      <c r="E4" s="100">
+      <c r="E4" s="99">
         <f t="shared" si="1"/>
         <v>0.93010000000000004</v>
       </c>
@@ -32082,7 +32198,7 @@
         <f>VLOOKUP(G$1,'HBC Rates'!$A$2:$B$15,2,FALSE)</f>
         <v>0.67700000000000005</v>
       </c>
-      <c r="H4" s="100">
+      <c r="H4" s="99">
         <f t="shared" si="2"/>
         <v>0.67700000000000005</v>
       </c>
@@ -32098,7 +32214,7 @@
         <f>VLOOKUP(K$1,'HBC Rates'!$A$2:$B$15,2,FALSE)</f>
         <v>0.56869999999999998</v>
       </c>
-      <c r="L4" s="100">
+      <c r="L4" s="99">
         <f t="shared" si="3"/>
         <v>0.56869999999999998</v>
       </c>
@@ -32106,23 +32222,23 @@
         <f>VLOOKUP(M$1,'HBC Rates'!$A$2:$B$15,2,FALSE)</f>
         <v>0.61580000000000001</v>
       </c>
-      <c r="N4" s="100">
+      <c r="N4" s="99">
         <f t="shared" si="0"/>
         <v>0.61580000000000001</v>
       </c>
-      <c r="O4" s="100">
+      <c r="O4" s="99">
         <f t="shared" si="0"/>
         <v>0.61580000000000001</v>
       </c>
-      <c r="P4" s="100">
+      <c r="P4" s="99">
         <f t="shared" si="0"/>
         <v>0.61580000000000001</v>
       </c>
-      <c r="Q4" s="100">
+      <c r="Q4" s="99">
         <f t="shared" si="0"/>
         <v>0.61580000000000001</v>
       </c>
-      <c r="R4" s="100">
+      <c r="R4" s="99">
         <f t="shared" si="0"/>
         <v>0.61580000000000001</v>
       </c>
@@ -32134,7 +32250,7 @@
         <f>VLOOKUP(T$1,'HBC Rates'!$A$2:$B$15,2,FALSE)</f>
         <v>0.94520000000000004</v>
       </c>
-      <c r="U4" s="100">
+      <c r="U4" s="99">
         <f t="shared" si="4"/>
         <v>0.94520000000000004</v>
       </c>
@@ -32155,18 +32271,18 @@
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A6" s="98" t="s">
+      <c r="A6" s="97" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A7" s="98" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A7" s="99" t="s">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A8" s="98" t="s">
         <v>179</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A8" s="99" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
@@ -32180,8 +32296,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="O1:AQ65"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="O1:AQ66"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="12" width="9" style="2"/>
@@ -36310,6 +36426,11 @@
         <v>241800</v>
       </c>
     </row>
+    <row r="66" spans="15:30" x14ac:dyDescent="0.25">
+      <c r="O66" s="108" t="s">
+        <v>199</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -36318,12 +36439,13 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AZ64"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:AZ65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="34" width="9" style="2"/>
-    <col min="35" max="42" width="9" style="7"/>
+    <col min="35" max="41" width="9" style="7"/>
+    <col min="42" max="42" width="10.42578125" style="7" customWidth="1"/>
     <col min="43" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -38705,6 +38827,11 @@
         <v>17</v>
       </c>
     </row>
+    <row r="65" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI65" s="108" t="s">
+        <v>200</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -38713,7 +38840,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:T15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -39185,7 +39312,7 @@
         <f>$G$8</f>
         <v>1.0967771874057404</v>
       </c>
-      <c r="D9" s="101">
+      <c r="D9" s="3">
         <f t="shared" si="4"/>
         <v>2023</v>
       </c>
@@ -39193,14 +39320,14 @@
       <c r="F9" s="45"/>
       <c r="G9" s="45"/>
       <c r="H9" s="45"/>
-      <c r="J9" s="101">
+      <c r="J9" s="3">
         <v>2023</v>
       </c>
       <c r="K9" s="20"/>
       <c r="L9" s="20"/>
       <c r="M9" s="20"/>
       <c r="N9" s="20"/>
-      <c r="P9" s="101">
+      <c r="P9" s="3">
         <f t="shared" si="3"/>
         <v>2023</v>
       </c>
@@ -39217,7 +39344,7 @@
         <f>$G$8</f>
         <v>1.0967771874057404</v>
       </c>
-      <c r="D10" s="101">
+      <c r="D10" s="3">
         <f t="shared" si="4"/>
         <v>2024</v>
       </c>
@@ -39225,14 +39352,14 @@
       <c r="F10" s="45"/>
       <c r="G10" s="45"/>
       <c r="H10" s="45"/>
-      <c r="J10" s="101">
+      <c r="J10" s="3">
         <v>2024</v>
       </c>
       <c r="K10" s="20"/>
       <c r="L10" s="20"/>
       <c r="M10" s="20"/>
       <c r="N10" s="20"/>
-      <c r="P10" s="101">
+      <c r="P10" s="3">
         <f t="shared" si="3"/>
         <v>2024</v>
       </c>
@@ -39248,6 +39375,12 @@
       <c r="B11" s="49">
         <f>$G$8</f>
         <v>1.0967771874057404</v>
+      </c>
+      <c r="K11" s="42" t="s">
+        <v>197</v>
+      </c>
+      <c r="Q11" s="42" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -39293,7 +39426,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <tabColor theme="0" tint="-0.499984740745262"/>
   </sheetPr>
@@ -39535,6 +39668,9 @@
         <f>$M$2</f>
         <v>0.62190000000000001</v>
       </c>
+      <c r="D4" s="107" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
@@ -39641,7 +39777,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <tabColor theme="0" tint="-0.499984740745262"/>
   </sheetPr>
@@ -39651,7 +39787,7 @@
     <col min="1" max="1" width="9" style="2"/>
     <col min="2" max="2" width="10.7109375" style="2" customWidth="1"/>
     <col min="3" max="5" width="9" style="2"/>
-    <col min="6" max="6" width="9" style="7"/>
+    <col min="6" max="6" width="10.42578125" style="7" customWidth="1"/>
     <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -39687,6 +39823,9 @@
       <c r="F2" s="67" t="s">
         <v>127</v>
       </c>
+      <c r="G2" s="42" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="3" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="68">
@@ -39780,7 +39919,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <tabColor theme="0" tint="-0.499984740745262"/>
   </sheetPr>
@@ -40135,7 +40274,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr>
     <tabColor theme="0" tint="-0.499984740745262"/>
   </sheetPr>
@@ -40343,19 +40482,19 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="108">
+      <c r="A13" s="102">
         <v>46006</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="J1" r:id="rId1"/>
-    <hyperlink ref="M1" r:id="rId2"/>
+    <hyperlink ref="J1" r:id="rId1" xr:uid="{00000000-0004-0000-0800-000000000000}"/>
+    <hyperlink ref="M1" r:id="rId2" xr:uid="{00000000-0004-0000-0800-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId3"/>

--- a/_Source - CollegeControlTotal - 2025-02-14_Start.xlsx
+++ b/_Source - CollegeControlTotal - 2025-02-14_Start.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\TDM-INP-College-Enrollment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E45F1F1-8399-4D09-8170-582139454AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B23857BC-5F36-4059-9261-D3CCE4DB276E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="728" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="728" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Export_ControlTot" sheetId="11" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="205">
   <si>
     <t>https://ushe.edu/institutional-data-resources-headcount/</t>
   </si>
@@ -684,6 +684,18 @@
   <si>
     <t>Project until 2060</t>
   </si>
+  <si>
+    <t>Brigham Young University</t>
+  </si>
+  <si>
+    <t>UofU</t>
+  </si>
+  <si>
+    <t>Salt Lake Community College</t>
+  </si>
+  <si>
+    <t>Ensign College</t>
+  </si>
 </sst>
 </file>
 
@@ -1014,7 +1026,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="2" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1276,6 +1288,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1285,14 +1305,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="3" builtinId="3"/>
@@ -22316,11 +22329,14 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="15" width="12.140625" style="7" customWidth="1"/>
-    <col min="16" max="21" width="9" style="7"/>
+    <col min="16" max="16" width="9" style="7"/>
+    <col min="17" max="17" width="12" style="7" customWidth="1"/>
+    <col min="18" max="18" width="29.42578125" style="7" customWidth="1"/>
+    <col min="19" max="21" width="9" style="7"/>
     <col min="22" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>112</v>
       </c>
@@ -22366,8 +22382,17 @@
       <c r="O1" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q1" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="110" t="s">
+        <v>201</v>
+      </c>
+      <c r="S1" s="7">
+        <v>230038</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1990</v>
       </c>
@@ -22427,8 +22452,17 @@
         <f>INDEX('Campus Enrol Disaggregation'!$P$5:$AC$65,MATCH(Export_ControlTot!$A2,'Campus Enrol Disaggregation'!$O$5:$O$65,0),MATCH(O$1,'Campus Enrol Disaggregation'!$P$4:$AC$4,0))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q2" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="R2" s="110" t="s">
+        <v>204</v>
+      </c>
+      <c r="S2" s="7">
+        <v>230418</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>1991</v>
       </c>
@@ -22488,8 +22522,17 @@
         <f>INDEX('Campus Enrol Disaggregation'!$P$5:$AC$65,MATCH(Export_ControlTot!$A3,'Campus Enrol Disaggregation'!$O$5:$O$65,0),MATCH(O$1,'Campus Enrol Disaggregation'!$P$4:$AC$4,0))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q3" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="R3" s="110" t="s">
+        <v>203</v>
+      </c>
+      <c r="S3" s="7">
+        <v>230746</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>1992</v>
       </c>
@@ -22549,8 +22592,17 @@
         <f>INDEX('Campus Enrol Disaggregation'!$P$5:$AC$65,MATCH(Export_ControlTot!$A4,'Campus Enrol Disaggregation'!$O$5:$O$65,0),MATCH(O$1,'Campus Enrol Disaggregation'!$P$4:$AC$4,0))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q4" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="R4" s="110" t="s">
+        <v>142</v>
+      </c>
+      <c r="S4" s="7">
+        <v>230764</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>1993</v>
       </c>
@@ -22610,8 +22662,17 @@
         <f>INDEX('Campus Enrol Disaggregation'!$P$5:$AC$65,MATCH(Export_ControlTot!$A5,'Campus Enrol Disaggregation'!$O$5:$O$65,0),MATCH(O$1,'Campus Enrol Disaggregation'!$P$4:$AC$4,0))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="R5" s="110" t="s">
+        <v>140</v>
+      </c>
+      <c r="S5" s="7">
+        <v>230737</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>1994</v>
       </c>
@@ -22671,8 +22732,17 @@
         <f>INDEX('Campus Enrol Disaggregation'!$P$5:$AC$65,MATCH(Export_ControlTot!$A6,'Campus Enrol Disaggregation'!$O$5:$O$65,0),MATCH(O$1,'Campus Enrol Disaggregation'!$P$4:$AC$4,0))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q6" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="R6" s="110" t="s">
+        <v>143</v>
+      </c>
+      <c r="S6" s="7">
+        <v>230782</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>1995</v>
       </c>
@@ -22732,8 +22802,17 @@
         <f>INDEX('Campus Enrol Disaggregation'!$P$5:$AC$65,MATCH(Export_ControlTot!$A7,'Campus Enrol Disaggregation'!$O$5:$O$65,0),MATCH(O$1,'Campus Enrol Disaggregation'!$P$4:$AC$4,0))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q7" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="R7" s="110" t="s">
+        <v>146</v>
+      </c>
+      <c r="S7" s="7">
+        <v>230807</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>1996</v>
       </c>
@@ -22794,7 +22873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>1997</v>
       </c>
@@ -22855,7 +22934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>1998</v>
       </c>
@@ -22916,7 +22995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>1999</v>
       </c>
@@ -22977,7 +23056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>2000</v>
       </c>
@@ -23038,7 +23117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>2001</v>
       </c>
@@ -23099,7 +23178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>2002</v>
       </c>
@@ -23160,7 +23239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>2003</v>
       </c>
@@ -23221,7 +23300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>2004</v>
       </c>
@@ -26117,7 +26196,7 @@
       <c r="A68" s="7">
         <v>2056</v>
       </c>
-      <c r="B68" s="108"/>
+      <c r="B68" s="105"/>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="7">
@@ -26140,7 +26219,7 @@
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="109" t="s">
+      <c r="A73" s="106" t="s">
         <v>198</v>
       </c>
     </row>
@@ -26177,30 +26256,30 @@
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
       <c r="J2" s="5"/>
-      <c r="Q2" s="103" t="s">
+      <c r="Q2" s="107" t="s">
         <v>1</v>
       </c>
-      <c r="R2" s="104"/>
-      <c r="S2" s="104"/>
-      <c r="T2" s="104"/>
-      <c r="U2" s="103" t="s">
+      <c r="R2" s="108"/>
+      <c r="S2" s="108"/>
+      <c r="T2" s="108"/>
+      <c r="U2" s="107" t="s">
         <v>2</v>
       </c>
-      <c r="V2" s="104"/>
-      <c r="W2" s="104"/>
-      <c r="X2" s="104"/>
-      <c r="Y2" s="103" t="s">
+      <c r="V2" s="108"/>
+      <c r="W2" s="108"/>
+      <c r="X2" s="108"/>
+      <c r="Y2" s="107" t="s">
         <v>3</v>
       </c>
-      <c r="Z2" s="104"/>
-      <c r="AA2" s="104"/>
-      <c r="AB2" s="104"/>
-      <c r="AC2" s="103" t="s">
+      <c r="Z2" s="108"/>
+      <c r="AA2" s="108"/>
+      <c r="AB2" s="108"/>
+      <c r="AC2" s="107" t="s">
         <v>4</v>
       </c>
-      <c r="AD2" s="104"/>
-      <c r="AE2" s="104"/>
-      <c r="AF2" s="104"/>
+      <c r="AD2" s="108"/>
+      <c r="AE2" s="108"/>
+      <c r="AF2" s="108"/>
     </row>
     <row r="3" spans="1:32" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -28004,7 +28083,7 @@
       <c r="A8" s="2">
         <v>2020</v>
       </c>
-      <c r="B8" s="106">
+      <c r="B8" s="103">
         <f>AVERAGE(B7,B9)</f>
         <v>1830</v>
       </c>
@@ -30004,196 +30083,196 @@
       </c>
     </row>
     <row r="31" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="105" t="s">
+      <c r="B31" s="109" t="s">
         <v>46</v>
       </c>
-      <c r="C31" s="105"/>
-      <c r="D31" s="105"/>
-      <c r="E31" s="105"/>
+      <c r="C31" s="109"/>
+      <c r="D31" s="109"/>
+      <c r="E31" s="109"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B32" s="105"/>
-      <c r="C32" s="105"/>
-      <c r="D32" s="105"/>
-      <c r="E32" s="105"/>
+      <c r="B32" s="109"/>
+      <c r="C32" s="109"/>
+      <c r="D32" s="109"/>
+      <c r="E32" s="109"/>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B33" s="105"/>
-      <c r="C33" s="105"/>
-      <c r="D33" s="105"/>
-      <c r="E33" s="105"/>
+      <c r="B33" s="109"/>
+      <c r="C33" s="109"/>
+      <c r="D33" s="109"/>
+      <c r="E33" s="109"/>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B34" s="105"/>
-      <c r="C34" s="105"/>
-      <c r="D34" s="105"/>
-      <c r="E34" s="105"/>
+      <c r="B34" s="109"/>
+      <c r="C34" s="109"/>
+      <c r="D34" s="109"/>
+      <c r="E34" s="109"/>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B35" s="105"/>
-      <c r="C35" s="105"/>
-      <c r="D35" s="105"/>
-      <c r="E35" s="105"/>
+      <c r="B35" s="109"/>
+      <c r="C35" s="109"/>
+      <c r="D35" s="109"/>
+      <c r="E35" s="109"/>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B36" s="105"/>
-      <c r="C36" s="105"/>
-      <c r="D36" s="105"/>
-      <c r="E36" s="105"/>
+      <c r="B36" s="109"/>
+      <c r="C36" s="109"/>
+      <c r="D36" s="109"/>
+      <c r="E36" s="109"/>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B37" s="105"/>
-      <c r="C37" s="105"/>
-      <c r="D37" s="105"/>
-      <c r="E37" s="105"/>
+      <c r="B37" s="109"/>
+      <c r="C37" s="109"/>
+      <c r="D37" s="109"/>
+      <c r="E37" s="109"/>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B38" s="105"/>
-      <c r="C38" s="105"/>
-      <c r="D38" s="105"/>
-      <c r="E38" s="105"/>
+      <c r="B38" s="109"/>
+      <c r="C38" s="109"/>
+      <c r="D38" s="109"/>
+      <c r="E38" s="109"/>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B39" s="105"/>
-      <c r="C39" s="105"/>
-      <c r="D39" s="105"/>
-      <c r="E39" s="105"/>
+      <c r="B39" s="109"/>
+      <c r="C39" s="109"/>
+      <c r="D39" s="109"/>
+      <c r="E39" s="109"/>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B40" s="105"/>
-      <c r="C40" s="105"/>
-      <c r="D40" s="105"/>
-      <c r="E40" s="105"/>
+      <c r="B40" s="109"/>
+      <c r="C40" s="109"/>
+      <c r="D40" s="109"/>
+      <c r="E40" s="109"/>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B41" s="105"/>
-      <c r="C41" s="105"/>
-      <c r="D41" s="105"/>
-      <c r="E41" s="105"/>
+      <c r="B41" s="109"/>
+      <c r="C41" s="109"/>
+      <c r="D41" s="109"/>
+      <c r="E41" s="109"/>
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B42" s="105"/>
-      <c r="C42" s="105"/>
-      <c r="D42" s="105"/>
-      <c r="E42" s="105"/>
+      <c r="B42" s="109"/>
+      <c r="C42" s="109"/>
+      <c r="D42" s="109"/>
+      <c r="E42" s="109"/>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B43" s="105"/>
-      <c r="C43" s="105"/>
-      <c r="D43" s="105"/>
-      <c r="E43" s="105"/>
+      <c r="B43" s="109"/>
+      <c r="C43" s="109"/>
+      <c r="D43" s="109"/>
+      <c r="E43" s="109"/>
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B44" s="105"/>
-      <c r="C44" s="105"/>
-      <c r="D44" s="105"/>
-      <c r="E44" s="105"/>
+      <c r="B44" s="109"/>
+      <c r="C44" s="109"/>
+      <c r="D44" s="109"/>
+      <c r="E44" s="109"/>
     </row>
     <row r="46" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B46" s="105" t="s">
+      <c r="B46" s="109" t="s">
         <v>44</v>
       </c>
-      <c r="C46" s="105"/>
-      <c r="D46" s="105"/>
-      <c r="E46" s="105"/>
+      <c r="C46" s="109"/>
+      <c r="D46" s="109"/>
+      <c r="E46" s="109"/>
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B47" s="105" t="s">
+      <c r="B47" s="109" t="s">
         <v>45</v>
       </c>
-      <c r="C47" s="105"/>
-      <c r="D47" s="105"/>
-      <c r="E47" s="105"/>
+      <c r="C47" s="109"/>
+      <c r="D47" s="109"/>
+      <c r="E47" s="109"/>
     </row>
     <row r="48" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B48" s="105"/>
-      <c r="C48" s="105"/>
-      <c r="D48" s="105"/>
-      <c r="E48" s="105"/>
+      <c r="B48" s="109"/>
+      <c r="C48" s="109"/>
+      <c r="D48" s="109"/>
+      <c r="E48" s="109"/>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B49" s="105"/>
-      <c r="C49" s="105"/>
-      <c r="D49" s="105"/>
-      <c r="E49" s="105"/>
+      <c r="B49" s="109"/>
+      <c r="C49" s="109"/>
+      <c r="D49" s="109"/>
+      <c r="E49" s="109"/>
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B50" s="105"/>
-      <c r="C50" s="105"/>
-      <c r="D50" s="105"/>
-      <c r="E50" s="105"/>
+      <c r="B50" s="109"/>
+      <c r="C50" s="109"/>
+      <c r="D50" s="109"/>
+      <c r="E50" s="109"/>
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B51" s="105"/>
-      <c r="C51" s="105"/>
-      <c r="D51" s="105"/>
-      <c r="E51" s="105"/>
+      <c r="B51" s="109"/>
+      <c r="C51" s="109"/>
+      <c r="D51" s="109"/>
+      <c r="E51" s="109"/>
     </row>
     <row r="52" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B52" s="105"/>
-      <c r="C52" s="105"/>
-      <c r="D52" s="105"/>
-      <c r="E52" s="105"/>
+      <c r="B52" s="109"/>
+      <c r="C52" s="109"/>
+      <c r="D52" s="109"/>
+      <c r="E52" s="109"/>
     </row>
     <row r="53" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B53" s="105"/>
-      <c r="C53" s="105"/>
-      <c r="D53" s="105"/>
-      <c r="E53" s="105"/>
+      <c r="B53" s="109"/>
+      <c r="C53" s="109"/>
+      <c r="D53" s="109"/>
+      <c r="E53" s="109"/>
     </row>
     <row r="54" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B54" s="105"/>
-      <c r="C54" s="105"/>
-      <c r="D54" s="105"/>
-      <c r="E54" s="105"/>
+      <c r="B54" s="109"/>
+      <c r="C54" s="109"/>
+      <c r="D54" s="109"/>
+      <c r="E54" s="109"/>
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B55" s="105"/>
-      <c r="C55" s="105"/>
-      <c r="D55" s="105"/>
-      <c r="E55" s="105"/>
+      <c r="B55" s="109"/>
+      <c r="C55" s="109"/>
+      <c r="D55" s="109"/>
+      <c r="E55" s="109"/>
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B56" s="105"/>
-      <c r="C56" s="105"/>
-      <c r="D56" s="105"/>
-      <c r="E56" s="105"/>
+      <c r="B56" s="109"/>
+      <c r="C56" s="109"/>
+      <c r="D56" s="109"/>
+      <c r="E56" s="109"/>
     </row>
     <row r="57" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B57" s="105"/>
-      <c r="C57" s="105"/>
-      <c r="D57" s="105"/>
-      <c r="E57" s="105"/>
+      <c r="B57" s="109"/>
+      <c r="C57" s="109"/>
+      <c r="D57" s="109"/>
+      <c r="E57" s="109"/>
     </row>
     <row r="58" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B58" s="105"/>
-      <c r="C58" s="105"/>
-      <c r="D58" s="105"/>
-      <c r="E58" s="105"/>
+      <c r="B58" s="109"/>
+      <c r="C58" s="109"/>
+      <c r="D58" s="109"/>
+      <c r="E58" s="109"/>
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B59" s="105"/>
-      <c r="C59" s="105"/>
-      <c r="D59" s="105"/>
-      <c r="E59" s="105"/>
+      <c r="B59" s="109"/>
+      <c r="C59" s="109"/>
+      <c r="D59" s="109"/>
+      <c r="E59" s="109"/>
     </row>
     <row r="60" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B60" s="105"/>
-      <c r="C60" s="105"/>
-      <c r="D60" s="105"/>
-      <c r="E60" s="105"/>
+      <c r="B60" s="109"/>
+      <c r="C60" s="109"/>
+      <c r="D60" s="109"/>
+      <c r="E60" s="109"/>
     </row>
     <row r="61" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B61" s="105"/>
-      <c r="C61" s="105"/>
-      <c r="D61" s="105"/>
-      <c r="E61" s="105"/>
+      <c r="B61" s="109"/>
+      <c r="C61" s="109"/>
+      <c r="D61" s="109"/>
+      <c r="E61" s="109"/>
     </row>
     <row r="62" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B62" s="105"/>
-      <c r="C62" s="105"/>
-      <c r="D62" s="105"/>
-      <c r="E62" s="105"/>
+      <c r="B62" s="109"/>
+      <c r="C62" s="109"/>
+      <c r="D62" s="109"/>
+      <c r="E62" s="109"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -36427,7 +36506,7 @@
       </c>
     </row>
     <row r="66" spans="15:30" x14ac:dyDescent="0.25">
-      <c r="O66" s="108" t="s">
+      <c r="O66" s="105" t="s">
         <v>199</v>
       </c>
     </row>
@@ -38828,7 +38907,7 @@
       </c>
     </row>
     <row r="65" spans="35:35" x14ac:dyDescent="0.25">
-      <c r="AI65" s="108" t="s">
+      <c r="AI65" s="105" t="s">
         <v>200</v>
       </c>
     </row>
@@ -39668,7 +39747,7 @@
         <f>$M$2</f>
         <v>0.62190000000000001</v>
       </c>
-      <c r="D4" s="107" t="s">
+      <c r="D4" s="104" t="s">
         <v>196</v>
       </c>
     </row>

--- a/_Source - CollegeControlTotal - 2025-02-14_Start.xlsx
+++ b/_Source - CollegeControlTotal - 2025-02-14_Start.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\TDM-INP-College-Enrollment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9E29411-E982-4B18-88BB-97CFBF29BEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F892C86D-C7E0-4B9E-9A8B-ED2BF8401368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="728" firstSheet="13" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="728" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Export_ControlTot" sheetId="11" r:id="rId1"/>
@@ -26,7 +26,7 @@
     <sheet name="BYU - Data USA Cart" sheetId="5" r:id="rId11"/>
     <sheet name="Westminster" sheetId="8" r:id="rId12"/>
     <sheet name="Ensign" sheetId="9" r:id="rId13"/>
-    <sheet name="Historic from 2019 RTP" sheetId="7" r:id="rId14"/>
+    <sheet name="Historic (IPEDS &amp; 2019 RTP)" sheetId="7" r:id="rId14"/>
     <sheet name="USHE 2020 Campus Totals" sheetId="3" r:id="rId15"/>
     <sheet name="MAG College Enrollment Forecast" sheetId="12" r:id="rId16"/>
   </sheets>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="206">
   <si>
     <t>https://ushe.edu/institutional-data-resources-headcount/</t>
   </si>
@@ -454,9 +454,6 @@
     <t>UVU_Vineyard</t>
   </si>
   <si>
-    <t>FTE</t>
-  </si>
-  <si>
     <t>Fall FTE by Division</t>
   </si>
   <si>
@@ -655,19 +652,7 @@
     <t>*USHE not currently releasing updates forecasts</t>
   </si>
   <si>
-    <t>Old Data</t>
-  </si>
-  <si>
-    <t>Might have to fill this.</t>
-  </si>
-  <si>
-    <t>Need to update</t>
-  </si>
-  <si>
     <t>Probably from College Survey</t>
-  </si>
-  <si>
-    <t>Not updated</t>
   </si>
   <si>
     <t>This has to update to 2055</t>
@@ -696,6 +681,24 @@
   <si>
     <t>Source: IPEDS as Calculated in 5-CollegeEnrollmentIPEDS.qmd (intermediate/Fall_Enrollment_1997_2023.csv), old data (&lt;2000 from 2019 RTP)</t>
   </si>
+  <si>
+    <t>Old Data from 2019 RTP:</t>
+  </si>
+  <si>
+    <t>(Data Last Updated: 2026/01/02)</t>
+  </si>
+  <si>
+    <t>Headcount (Source: IPEDS/5-CollegeEnrollmentIPEDS.qmd)</t>
+  </si>
+  <si>
+    <t>FTE (Source: IPEDS/5-CollegeEnrollmentIPEDS.qmd)</t>
+  </si>
+  <si>
+    <t>Source: from 2019 RTP (Not used in calculation)</t>
+  </si>
+  <si>
+    <t>Old</t>
+  </si>
 </sst>
 </file>
 
@@ -709,7 +712,7 @@
     <numFmt numFmtId="167" formatCode="0.000"/>
     <numFmt numFmtId="168" formatCode="#,##0;\-#,##0;\-"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -835,8 +838,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -888,12 +898,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1215,12 +1219,6 @@
     <xf numFmtId="168" fontId="15" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1273,7 +1271,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1305,6 +1303,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="3" builtinId="3"/>
@@ -22385,7 +22385,7 @@
         <v>15</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="S1" s="7">
         <v>230038</v>
@@ -22455,7 +22455,7 @@
         <v>16</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="S2" s="7">
         <v>230418</v>
@@ -22525,7 +22525,7 @@
         <v>4</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="S3" s="7">
         <v>230746</v>
@@ -22592,10 +22592,10 @@
         <v>0</v>
       </c>
       <c r="Q4" s="11" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S4" s="7">
         <v>230764</v>
@@ -22665,7 +22665,7 @@
         <v>3</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="S5" s="7">
         <v>230737</v>
@@ -22735,7 +22735,7 @@
         <v>2</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="S6" s="7">
         <v>230782</v>
@@ -22805,7 +22805,7 @@
         <v>17</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="S7" s="7">
         <v>230807</v>
@@ -26195,7 +26195,7 @@
       <c r="A68" s="7">
         <v>2056</v>
       </c>
-      <c r="B68" s="105"/>
+      <c r="B68" s="103"/>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="7">
@@ -26218,8 +26218,8 @@
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="106" t="s">
-        <v>196</v>
+      <c r="A73" s="104" t="s">
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -26246,39 +26246,39 @@
         <v>7</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
       <c r="J2" s="5"/>
-      <c r="Q2" s="107" t="s">
+      <c r="Q2" s="105" t="s">
         <v>1</v>
       </c>
-      <c r="R2" s="108"/>
-      <c r="S2" s="108"/>
-      <c r="T2" s="108"/>
-      <c r="U2" s="107" t="s">
+      <c r="R2" s="106"/>
+      <c r="S2" s="106"/>
+      <c r="T2" s="106"/>
+      <c r="U2" s="105" t="s">
         <v>2</v>
       </c>
-      <c r="V2" s="108"/>
-      <c r="W2" s="108"/>
-      <c r="X2" s="108"/>
-      <c r="Y2" s="107" t="s">
+      <c r="V2" s="106"/>
+      <c r="W2" s="106"/>
+      <c r="X2" s="106"/>
+      <c r="Y2" s="105" t="s">
         <v>3</v>
       </c>
-      <c r="Z2" s="108"/>
-      <c r="AA2" s="108"/>
-      <c r="AB2" s="108"/>
-      <c r="AC2" s="107" t="s">
+      <c r="Z2" s="106"/>
+      <c r="AA2" s="106"/>
+      <c r="AB2" s="106"/>
+      <c r="AC2" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="AD2" s="108"/>
-      <c r="AE2" s="108"/>
-      <c r="AF2" s="108"/>
+      <c r="AD2" s="106"/>
+      <c r="AE2" s="106"/>
+      <c r="AF2" s="106"/>
     </row>
     <row r="3" spans="1:32" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -26443,8 +26443,8 @@
         <v>2017</v>
       </c>
       <c r="K5" s="26">
-        <f>SUM($R5:$U5)</f>
-        <v>19335.3</v>
+        <f>SUM($Q5:$T5)</f>
+        <v>22269.399999999998</v>
       </c>
       <c r="L5" s="26">
         <f>SUM($U5:$X5)</f>
@@ -26529,8 +26529,8 @@
         <v>2018</v>
       </c>
       <c r="K6" s="26">
-        <f t="shared" ref="K6:K12" si="0">SUM($R6:$U6)</f>
-        <v>19516.7</v>
+        <f t="shared" ref="K6:K12" si="0">SUM($Q6:$T6)</f>
+        <v>22358.9</v>
       </c>
       <c r="L6" s="26">
         <f t="shared" ref="L6:L12" si="1">SUM($U6:$X6)</f>
@@ -26616,7 +26616,7 @@
       </c>
       <c r="K7" s="26">
         <f t="shared" si="0"/>
-        <v>19427.45</v>
+        <v>22130.05</v>
       </c>
       <c r="L7" s="26">
         <f t="shared" si="1"/>
@@ -26704,7 +26704,7 @@
       </c>
       <c r="K8" s="26">
         <f t="shared" si="0"/>
-        <v>19400.150000000001</v>
+        <v>22041.05</v>
       </c>
       <c r="L8" s="26">
         <f t="shared" si="1"/>
@@ -26792,7 +26792,7 @@
       </c>
       <c r="K9" s="26">
         <f t="shared" si="0"/>
-        <v>18694.25</v>
+        <v>21849.75</v>
       </c>
       <c r="L9" s="26">
         <f t="shared" si="1"/>
@@ -26880,7 +26880,7 @@
       </c>
       <c r="K10" s="26">
         <f t="shared" si="0"/>
-        <v>17695.349999999999</v>
+        <v>21041.149999999998</v>
       </c>
       <c r="L10" s="26">
         <f t="shared" si="1"/>
@@ -26968,7 +26968,7 @@
       </c>
       <c r="K11" s="26">
         <f t="shared" si="0"/>
-        <v>17537.650000000001</v>
+        <v>21107.15</v>
       </c>
       <c r="L11" s="26">
         <f t="shared" si="1"/>
@@ -26982,7 +26982,7 @@
         <f t="shared" si="3"/>
         <v>5949</v>
       </c>
-      <c r="P11" s="101">
+      <c r="P11" s="99">
         <v>2023</v>
       </c>
       <c r="Q11" s="43">
@@ -27042,12 +27042,21 @@
       <c r="E12" s="18">
         <v>27437</v>
       </c>
+      <c r="F12" s="18">
+        <v>7558</v>
+      </c>
+      <c r="G12" s="18">
+        <v>7770</v>
+      </c>
+      <c r="H12" s="18">
+        <v>6735</v>
+      </c>
       <c r="J12" s="3">
         <v>2024</v>
       </c>
       <c r="K12" s="26">
         <f t="shared" si="0"/>
-        <v>18064.650000000001</v>
+        <v>21974.45</v>
       </c>
       <c r="L12" s="26">
         <f t="shared" si="1"/>
@@ -27061,7 +27070,7 @@
         <f t="shared" si="3"/>
         <v>6142</v>
       </c>
-      <c r="P12" s="101">
+      <c r="P12" s="99">
         <v>2024</v>
       </c>
       <c r="Q12" s="43">
@@ -27106,8 +27115,25 @@
       <c r="AF12" s="44"/>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="F13" s="42" t="s">
-        <v>192</v>
+      <c r="A13" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B13" s="18">
+        <v>38257</v>
+      </c>
+      <c r="C13" s="18">
+        <v>33293</v>
+      </c>
+      <c r="D13" s="18">
+        <v>48670</v>
+      </c>
+      <c r="E13" s="18">
+        <v>31473</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
@@ -27212,13 +27238,13 @@
         <v>81</v>
       </c>
       <c r="L1" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="M1" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="M1" s="16" t="s">
+      <c r="N1" s="16" t="s">
         <v>180</v>
-      </c>
-      <c r="N1" s="16" t="s">
-        <v>181</v>
       </c>
       <c r="O1" s="16" t="s">
         <v>80</v>
@@ -27248,13 +27274,13 @@
         <v>72</v>
       </c>
       <c r="X1" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y1" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="Y1" s="16" t="s">
+      <c r="Z1" s="16" t="s">
         <v>185</v>
-      </c>
-      <c r="Z1" s="16" t="s">
-        <v>186</v>
       </c>
       <c r="AA1" s="16" t="s">
         <v>71</v>
@@ -27284,13 +27310,13 @@
         <v>63</v>
       </c>
       <c r="AJ1" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="AK1" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="AK1" s="16" t="s">
+      <c r="AL1" s="16" t="s">
         <v>188</v>
-      </c>
-      <c r="AL1" s="16" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="2" spans="1:38" x14ac:dyDescent="0.25">
@@ -27630,10 +27656,10 @@
     </row>
     <row r="8" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -27711,7 +27737,7 @@
       <c r="N3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="V3" s="100">
+      <c r="V3" s="98">
         <v>45702</v>
       </c>
     </row>
@@ -28082,7 +28108,7 @@
       <c r="A8" s="2">
         <v>2020</v>
       </c>
-      <c r="B8" s="103">
+      <c r="B8" s="101">
         <f>AVERAGE(B7,B9)</f>
         <v>1830</v>
       </c>
@@ -28165,8 +28191,8 @@
       <c r="H1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="95" t="s">
-        <v>204</v>
+      <c r="I1" s="93" t="s">
+        <v>199</v>
       </c>
       <c r="K1" s="7"/>
       <c r="L1" s="7"/>
@@ -29899,7 +29925,8 @@
     <col min="3" max="3" width="54" style="11" customWidth="1"/>
     <col min="4" max="4" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="2"/>
+    <col min="6" max="6" width="22.7109375" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -29918,19 +29945,19 @@
       <c r="E1" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="F1" s="95" t="s">
-        <v>203</v>
+      <c r="F1" s="93" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A2" s="40"/>
-      <c r="B2" s="83" t="s">
+      <c r="B2" s="81" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="84" t="s">
+      <c r="C2" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="85">
+      <c r="D2" s="83">
         <f>E2/SUMIFS($E$2:$E$28,$B$2:$B$28,B2)</f>
         <v>0</v>
       </c>
@@ -29938,7 +29965,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="42" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="G2" s="2">
         <v>6</v>
@@ -29948,13 +29975,13 @@
       <c r="A3" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="B3" s="83" t="s">
+      <c r="B3" s="81" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="86" t="s">
+      <c r="C3" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="87">
+      <c r="D3" s="85">
         <f t="shared" ref="D3:D28" si="0">E3/SUMIFS($E$2:$E$28,$B$2:$B$28,B3)</f>
         <v>0.68409986859395533</v>
       </c>
@@ -29967,13 +29994,13 @@
     </row>
     <row r="4" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A4" s="40"/>
-      <c r="B4" s="83" t="s">
+      <c r="B4" s="81" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="86" t="s">
+      <c r="C4" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="87">
+      <c r="D4" s="85">
         <f t="shared" si="0"/>
         <v>4.4240035041611912E-3</v>
       </c>
@@ -29986,13 +30013,13 @@
     </row>
     <row r="5" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A5" s="40"/>
-      <c r="B5" s="83" t="s">
+      <c r="B5" s="81" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="86" t="s">
+      <c r="C5" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="87">
+      <c r="D5" s="85">
         <f t="shared" si="0"/>
         <v>3.9903635567236091E-2</v>
       </c>
@@ -30007,13 +30034,13 @@
       <c r="A6" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="83" t="s">
+      <c r="B6" s="81" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="86" t="s">
+      <c r="C6" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="87">
+      <c r="D6" s="85">
         <f t="shared" si="0"/>
         <v>0.13337713534822601</v>
       </c>
@@ -30028,13 +30055,13 @@
       <c r="A7" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="B7" s="83" t="s">
+      <c r="B7" s="81" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="86" t="s">
+      <c r="C7" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="87">
+      <c r="D7" s="85">
         <f t="shared" si="0"/>
         <v>1.6162943495400789E-2</v>
       </c>
@@ -30047,13 +30074,13 @@
     </row>
     <row r="8" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A8" s="40"/>
-      <c r="B8" s="83" t="s">
+      <c r="B8" s="81" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="86" t="s">
+      <c r="C8" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="87">
+      <c r="D8" s="85">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -30066,13 +30093,13 @@
     </row>
     <row r="9" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="40"/>
-      <c r="B9" s="83" t="s">
+      <c r="B9" s="81" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="86" t="s">
+      <c r="C9" s="84" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="87">
+      <c r="D9" s="85">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -30087,13 +30114,13 @@
       <c r="A10" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="83" t="s">
+      <c r="B10" s="81" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="86" t="s">
+      <c r="C10" s="84" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="87">
+      <c r="D10" s="85">
         <f t="shared" si="0"/>
         <v>0.10175208059570741</v>
       </c>
@@ -30106,13 +30133,13 @@
     </row>
     <row r="11" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A11" s="40"/>
-      <c r="B11" s="83" t="s">
+      <c r="B11" s="81" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="86" t="s">
+      <c r="C11" s="84" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="87">
+      <c r="D11" s="85">
         <f t="shared" si="0"/>
         <v>1.4586070959264126E-2</v>
       </c>
@@ -30125,13 +30152,13 @@
     </row>
     <row r="12" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A12" s="40"/>
-      <c r="B12" s="88" t="s">
+      <c r="B12" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="89" t="s">
+      <c r="C12" s="87" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="90">
+      <c r="D12" s="88">
         <f t="shared" si="0"/>
         <v>5.6942619360490585E-3</v>
       </c>
@@ -30144,13 +30171,13 @@
     </row>
     <row r="13" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A13" s="40"/>
-      <c r="B13" s="83" t="s">
+      <c r="B13" s="81" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="91" t="s">
+      <c r="C13" s="89" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="92">
+      <c r="D13" s="90">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -30163,13 +30190,13 @@
     </row>
     <row r="14" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A14" s="40"/>
-      <c r="B14" s="83" t="s">
+      <c r="B14" s="81" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="86" t="s">
+      <c r="C14" s="84" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="87">
+      <c r="D14" s="85">
         <f t="shared" si="0"/>
         <v>0.47182175622542594</v>
       </c>
@@ -30182,13 +30209,13 @@
     </row>
     <row r="15" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A15" s="40"/>
-      <c r="B15" s="83" t="s">
+      <c r="B15" s="81" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="86" t="s">
+      <c r="C15" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="87">
+      <c r="D15" s="85">
         <f t="shared" si="0"/>
         <v>0.19528178243774574</v>
       </c>
@@ -30201,13 +30228,13 @@
     </row>
     <row r="16" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A16" s="40"/>
-      <c r="B16" s="83" t="s">
+      <c r="B16" s="81" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="86" t="s">
+      <c r="C16" s="84" t="s">
         <v>34</v>
       </c>
-      <c r="D16" s="87">
+      <c r="D16" s="85">
         <f t="shared" si="0"/>
         <v>2.8833551769331587E-2</v>
       </c>
@@ -30220,13 +30247,13 @@
     </row>
     <row r="17" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A17" s="40"/>
-      <c r="B17" s="83" t="s">
+      <c r="B17" s="81" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="86" t="s">
+      <c r="C17" s="84" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="87">
+      <c r="D17" s="85">
         <f t="shared" si="0"/>
         <v>0.12844036697247707</v>
       </c>
@@ -30239,13 +30266,13 @@
     </row>
     <row r="18" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A18" s="40"/>
-      <c r="B18" s="88" t="s">
+      <c r="B18" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="89" t="s">
+      <c r="C18" s="87" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="90">
+      <c r="D18" s="88">
         <f t="shared" si="0"/>
         <v>0.17562254259501967</v>
       </c>
@@ -30260,13 +30287,13 @@
       <c r="A19" s="40" t="s">
         <v>100</v>
       </c>
-      <c r="B19" s="83" t="s">
+      <c r="B19" s="81" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="91" t="s">
+      <c r="C19" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="92">
+      <c r="D19" s="90">
         <f t="shared" si="0"/>
         <v>0.96822824938358576</v>
       </c>
@@ -30279,13 +30306,13 @@
     </row>
     <row r="20" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A20" s="40"/>
-      <c r="B20" s="88" t="s">
+      <c r="B20" s="86" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="89" t="s">
+      <c r="C20" s="87" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="90">
+      <c r="D20" s="88">
         <f t="shared" si="0"/>
         <v>3.1771750616414234E-2</v>
       </c>
@@ -30300,13 +30327,13 @@
       <c r="A21" s="40" t="s">
         <v>101</v>
       </c>
-      <c r="B21" s="93" t="s">
+      <c r="B21" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="C21" s="93" t="s">
+      <c r="C21" s="91" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="94">
+      <c r="D21" s="92">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -30319,13 +30346,13 @@
     </row>
     <row r="22" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A22" s="40"/>
-      <c r="B22" s="83" t="s">
+      <c r="B22" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="91" t="s">
+      <c r="C22" s="89" t="s">
         <v>39</v>
       </c>
-      <c r="D22" s="92">
+      <c r="D22" s="90">
         <f t="shared" si="0"/>
         <v>7.5146771037181998E-3</v>
       </c>
@@ -30340,13 +30367,13 @@
       <c r="A23" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="B23" s="83" t="s">
+      <c r="B23" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="86" t="s">
+      <c r="C23" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="87">
+      <c r="D23" s="85">
         <f t="shared" si="0"/>
         <v>0.81142857142857139</v>
       </c>
@@ -30359,13 +30386,13 @@
     </row>
     <row r="24" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A24" s="40"/>
-      <c r="B24" s="83" t="s">
+      <c r="B24" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="86" t="s">
+      <c r="C24" s="84" t="s">
         <v>40</v>
       </c>
-      <c r="D24" s="87">
+      <c r="D24" s="85">
         <f t="shared" si="0"/>
         <v>4.8532289628180035E-3</v>
       </c>
@@ -30378,13 +30405,13 @@
     </row>
     <row r="25" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A25" s="40"/>
-      <c r="B25" s="83" t="s">
+      <c r="B25" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="C25" s="86" t="s">
+      <c r="C25" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="D25" s="87">
+      <c r="D25" s="85">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -30399,13 +30426,13 @@
       <c r="A26" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="B26" s="83" t="s">
+      <c r="B26" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="C26" s="86" t="s">
+      <c r="C26" s="84" t="s">
         <v>41</v>
       </c>
-      <c r="D26" s="87">
+      <c r="D26" s="85">
         <f t="shared" si="0"/>
         <v>0.16281800391389434</v>
       </c>
@@ -30418,13 +30445,13 @@
     </row>
     <row r="27" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A27" s="40"/>
-      <c r="B27" s="83" t="s">
+      <c r="B27" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="C27" s="86" t="s">
+      <c r="C27" s="84" t="s">
         <v>42</v>
       </c>
-      <c r="D27" s="87">
+      <c r="D27" s="85">
         <f t="shared" si="0"/>
         <v>1.3385518590998043E-2</v>
       </c>
@@ -30437,13 +30464,13 @@
     </row>
     <row r="28" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A28" s="40"/>
-      <c r="B28" s="88" t="s">
+      <c r="B28" s="86" t="s">
         <v>2</v>
       </c>
-      <c r="C28" s="89" t="s">
+      <c r="C28" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="D28" s="90">
+      <c r="D28" s="88">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -30455,196 +30482,196 @@
       </c>
     </row>
     <row r="31" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="109" t="s">
+      <c r="B31" s="107" t="s">
         <v>46</v>
       </c>
-      <c r="C31" s="109"/>
-      <c r="D31" s="109"/>
-      <c r="E31" s="109"/>
+      <c r="C31" s="107"/>
+      <c r="D31" s="107"/>
+      <c r="E31" s="107"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B32" s="109"/>
-      <c r="C32" s="109"/>
-      <c r="D32" s="109"/>
-      <c r="E32" s="109"/>
+      <c r="B32" s="107"/>
+      <c r="C32" s="107"/>
+      <c r="D32" s="107"/>
+      <c r="E32" s="107"/>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B33" s="109"/>
-      <c r="C33" s="109"/>
-      <c r="D33" s="109"/>
-      <c r="E33" s="109"/>
+      <c r="B33" s="107"/>
+      <c r="C33" s="107"/>
+      <c r="D33" s="107"/>
+      <c r="E33" s="107"/>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B34" s="109"/>
-      <c r="C34" s="109"/>
-      <c r="D34" s="109"/>
-      <c r="E34" s="109"/>
+      <c r="B34" s="107"/>
+      <c r="C34" s="107"/>
+      <c r="D34" s="107"/>
+      <c r="E34" s="107"/>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B35" s="109"/>
-      <c r="C35" s="109"/>
-      <c r="D35" s="109"/>
-      <c r="E35" s="109"/>
+      <c r="B35" s="107"/>
+      <c r="C35" s="107"/>
+      <c r="D35" s="107"/>
+      <c r="E35" s="107"/>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B36" s="109"/>
-      <c r="C36" s="109"/>
-      <c r="D36" s="109"/>
-      <c r="E36" s="109"/>
+      <c r="B36" s="107"/>
+      <c r="C36" s="107"/>
+      <c r="D36" s="107"/>
+      <c r="E36" s="107"/>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B37" s="109"/>
-      <c r="C37" s="109"/>
-      <c r="D37" s="109"/>
-      <c r="E37" s="109"/>
+      <c r="B37" s="107"/>
+      <c r="C37" s="107"/>
+      <c r="D37" s="107"/>
+      <c r="E37" s="107"/>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B38" s="109"/>
-      <c r="C38" s="109"/>
-      <c r="D38" s="109"/>
-      <c r="E38" s="109"/>
+      <c r="B38" s="107"/>
+      <c r="C38" s="107"/>
+      <c r="D38" s="107"/>
+      <c r="E38" s="107"/>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B39" s="109"/>
-      <c r="C39" s="109"/>
-      <c r="D39" s="109"/>
-      <c r="E39" s="109"/>
+      <c r="B39" s="107"/>
+      <c r="C39" s="107"/>
+      <c r="D39" s="107"/>
+      <c r="E39" s="107"/>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B40" s="109"/>
-      <c r="C40" s="109"/>
-      <c r="D40" s="109"/>
-      <c r="E40" s="109"/>
+      <c r="B40" s="107"/>
+      <c r="C40" s="107"/>
+      <c r="D40" s="107"/>
+      <c r="E40" s="107"/>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B41" s="109"/>
-      <c r="C41" s="109"/>
-      <c r="D41" s="109"/>
-      <c r="E41" s="109"/>
+      <c r="B41" s="107"/>
+      <c r="C41" s="107"/>
+      <c r="D41" s="107"/>
+      <c r="E41" s="107"/>
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B42" s="109"/>
-      <c r="C42" s="109"/>
-      <c r="D42" s="109"/>
-      <c r="E42" s="109"/>
+      <c r="B42" s="107"/>
+      <c r="C42" s="107"/>
+      <c r="D42" s="107"/>
+      <c r="E42" s="107"/>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B43" s="109"/>
-      <c r="C43" s="109"/>
-      <c r="D43" s="109"/>
-      <c r="E43" s="109"/>
+      <c r="B43" s="107"/>
+      <c r="C43" s="107"/>
+      <c r="D43" s="107"/>
+      <c r="E43" s="107"/>
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B44" s="109"/>
-      <c r="C44" s="109"/>
-      <c r="D44" s="109"/>
-      <c r="E44" s="109"/>
+      <c r="B44" s="107"/>
+      <c r="C44" s="107"/>
+      <c r="D44" s="107"/>
+      <c r="E44" s="107"/>
     </row>
     <row r="46" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B46" s="109" t="s">
+      <c r="B46" s="107" t="s">
         <v>44</v>
       </c>
-      <c r="C46" s="109"/>
-      <c r="D46" s="109"/>
-      <c r="E46" s="109"/>
+      <c r="C46" s="107"/>
+      <c r="D46" s="107"/>
+      <c r="E46" s="107"/>
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B47" s="109" t="s">
+      <c r="B47" s="107" t="s">
         <v>45</v>
       </c>
-      <c r="C47" s="109"/>
-      <c r="D47" s="109"/>
-      <c r="E47" s="109"/>
+      <c r="C47" s="107"/>
+      <c r="D47" s="107"/>
+      <c r="E47" s="107"/>
     </row>
     <row r="48" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B48" s="109"/>
-      <c r="C48" s="109"/>
-      <c r="D48" s="109"/>
-      <c r="E48" s="109"/>
+      <c r="B48" s="107"/>
+      <c r="C48" s="107"/>
+      <c r="D48" s="107"/>
+      <c r="E48" s="107"/>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B49" s="109"/>
-      <c r="C49" s="109"/>
-      <c r="D49" s="109"/>
-      <c r="E49" s="109"/>
+      <c r="B49" s="107"/>
+      <c r="C49" s="107"/>
+      <c r="D49" s="107"/>
+      <c r="E49" s="107"/>
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B50" s="109"/>
-      <c r="C50" s="109"/>
-      <c r="D50" s="109"/>
-      <c r="E50" s="109"/>
+      <c r="B50" s="107"/>
+      <c r="C50" s="107"/>
+      <c r="D50" s="107"/>
+      <c r="E50" s="107"/>
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B51" s="109"/>
-      <c r="C51" s="109"/>
-      <c r="D51" s="109"/>
-      <c r="E51" s="109"/>
+      <c r="B51" s="107"/>
+      <c r="C51" s="107"/>
+      <c r="D51" s="107"/>
+      <c r="E51" s="107"/>
     </row>
     <row r="52" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B52" s="109"/>
-      <c r="C52" s="109"/>
-      <c r="D52" s="109"/>
-      <c r="E52" s="109"/>
+      <c r="B52" s="107"/>
+      <c r="C52" s="107"/>
+      <c r="D52" s="107"/>
+      <c r="E52" s="107"/>
     </row>
     <row r="53" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B53" s="109"/>
-      <c r="C53" s="109"/>
-      <c r="D53" s="109"/>
-      <c r="E53" s="109"/>
+      <c r="B53" s="107"/>
+      <c r="C53" s="107"/>
+      <c r="D53" s="107"/>
+      <c r="E53" s="107"/>
     </row>
     <row r="54" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B54" s="109"/>
-      <c r="C54" s="109"/>
-      <c r="D54" s="109"/>
-      <c r="E54" s="109"/>
+      <c r="B54" s="107"/>
+      <c r="C54" s="107"/>
+      <c r="D54" s="107"/>
+      <c r="E54" s="107"/>
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B55" s="109"/>
-      <c r="C55" s="109"/>
-      <c r="D55" s="109"/>
-      <c r="E55" s="109"/>
+      <c r="B55" s="107"/>
+      <c r="C55" s="107"/>
+      <c r="D55" s="107"/>
+      <c r="E55" s="107"/>
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B56" s="109"/>
-      <c r="C56" s="109"/>
-      <c r="D56" s="109"/>
-      <c r="E56" s="109"/>
+      <c r="B56" s="107"/>
+      <c r="C56" s="107"/>
+      <c r="D56" s="107"/>
+      <c r="E56" s="107"/>
     </row>
     <row r="57" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B57" s="109"/>
-      <c r="C57" s="109"/>
-      <c r="D57" s="109"/>
-      <c r="E57" s="109"/>
+      <c r="B57" s="107"/>
+      <c r="C57" s="107"/>
+      <c r="D57" s="107"/>
+      <c r="E57" s="107"/>
     </row>
     <row r="58" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B58" s="109"/>
-      <c r="C58" s="109"/>
-      <c r="D58" s="109"/>
-      <c r="E58" s="109"/>
+      <c r="B58" s="107"/>
+      <c r="C58" s="107"/>
+      <c r="D58" s="107"/>
+      <c r="E58" s="107"/>
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B59" s="109"/>
-      <c r="C59" s="109"/>
-      <c r="D59" s="109"/>
-      <c r="E59" s="109"/>
+      <c r="B59" s="107"/>
+      <c r="C59" s="107"/>
+      <c r="D59" s="107"/>
+      <c r="E59" s="107"/>
     </row>
     <row r="60" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B60" s="109"/>
-      <c r="C60" s="109"/>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
+      <c r="B60" s="107"/>
+      <c r="C60" s="107"/>
+      <c r="D60" s="107"/>
+      <c r="E60" s="107"/>
     </row>
     <row r="61" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B61" s="109"/>
-      <c r="C61" s="109"/>
-      <c r="D61" s="109"/>
-      <c r="E61" s="109"/>
+      <c r="B61" s="107"/>
+      <c r="C61" s="107"/>
+      <c r="D61" s="107"/>
+      <c r="E61" s="107"/>
     </row>
     <row r="62" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B62" s="109"/>
-      <c r="C62" s="109"/>
-      <c r="D62" s="109"/>
-      <c r="E62" s="109"/>
+      <c r="B62" s="107"/>
+      <c r="C62" s="107"/>
+      <c r="D62" s="107"/>
+      <c r="E62" s="107"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -32345,80 +32372,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
-        <v>175</v>
-      </c>
-      <c r="B1" s="96" t="s">
+      <c r="A1" s="94" t="s">
+        <v>174</v>
+      </c>
+      <c r="B1" s="94" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="96" t="s">
+      <c r="C1" s="94" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="96" t="s">
+      <c r="D1" s="94" t="s">
         <v>100</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="F1" s="94" t="s">
+        <v>107</v>
+      </c>
+      <c r="G1" s="94" t="s">
+        <v>106</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="F1" s="96" t="s">
-        <v>107</v>
-      </c>
-      <c r="G1" s="96" t="s">
-        <v>106</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="I1" s="96" t="s">
+      <c r="I1" s="94" t="s">
         <v>52</v>
       </c>
-      <c r="J1" s="96" t="s">
+      <c r="J1" s="94" t="s">
         <v>55</v>
       </c>
-      <c r="K1" s="96" t="s">
+      <c r="K1" s="94" t="s">
         <v>53</v>
       </c>
       <c r="L1" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="M1" s="94" t="s">
+        <v>54</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="M1" s="96" t="s">
-        <v>54</v>
-      </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="R1" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="S1" s="96" t="s">
+      <c r="S1" s="94" t="s">
         <v>15</v>
       </c>
-      <c r="T1" s="96" t="s">
+      <c r="T1" s="94" t="s">
         <v>101</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="V1" s="96" t="s">
+        <v>162</v>
+      </c>
+      <c r="V1" s="94" t="s">
         <v>121</v>
       </c>
-      <c r="W1" s="96" t="s">
+      <c r="W1" s="94" t="s">
         <v>123</v>
       </c>
-      <c r="X1" s="96" t="s">
+      <c r="X1" s="94" t="s">
         <v>122</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32437,7 +32464,7 @@
         <f>VLOOKUP(D1,'calc%concurrent'!$A$2:$B$15,2,FALSE)</f>
         <v>2.6040514489776623E-2</v>
       </c>
-      <c r="E2" s="99">
+      <c r="E2" s="97">
         <f>D2</f>
         <v>2.6040514489776623E-2</v>
       </c>
@@ -32449,7 +32476,7 @@
         <f>VLOOKUP(G1,'calc%concurrent'!$A$2:$B$15,2,FALSE)</f>
         <v>0.30851477449455678</v>
       </c>
-      <c r="H2" s="99">
+      <c r="H2" s="97">
         <f>G2</f>
         <v>0.30851477449455678</v>
       </c>
@@ -32465,7 +32492,7 @@
         <f>VLOOKUP(K1,'calc%concurrent'!$A$2:$B$15,2,FALSE)</f>
         <v>0.34092450566077115</v>
       </c>
-      <c r="L2" s="99">
+      <c r="L2" s="97">
         <f>K2</f>
         <v>0.34092450566077115</v>
       </c>
@@ -32473,23 +32500,23 @@
         <f>VLOOKUP(M1,'calc%concurrent'!$A$2:$B$15,2,FALSE)</f>
         <v>0.34092450566077115</v>
       </c>
-      <c r="N2" s="99">
+      <c r="N2" s="97">
         <f t="shared" ref="N2:R4" si="0">M2</f>
         <v>0.34092450566077115</v>
       </c>
-      <c r="O2" s="99">
+      <c r="O2" s="97">
         <f t="shared" si="0"/>
         <v>0.34092450566077115</v>
       </c>
-      <c r="P2" s="99">
+      <c r="P2" s="97">
         <f t="shared" si="0"/>
         <v>0.34092450566077115</v>
       </c>
-      <c r="Q2" s="99">
+      <c r="Q2" s="97">
         <f t="shared" si="0"/>
         <v>0.34092450566077115</v>
       </c>
-      <c r="R2" s="99">
+      <c r="R2" s="97">
         <f t="shared" si="0"/>
         <v>0.34092450566077115</v>
       </c>
@@ -32501,7 +32528,7 @@
         <f>VLOOKUP(T1,'calc%concurrent'!$A$2:$B$15,2,FALSE)</f>
         <v>0.26992028734364659</v>
       </c>
-      <c r="U2" s="99">
+      <c r="U2" s="97">
         <f>T2</f>
         <v>0.26992028734364659</v>
       </c>
@@ -32518,7 +32545,7 @@
         <v>0.26992028734364659</v>
       </c>
       <c r="Y2" s="53" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32527,98 +32554,98 @@
       </c>
       <c r="B3" s="54">
         <f>VLOOKUP(B$1,'FTE Rate Calcs'!$A$2:$B$15,2,FALSE)</f>
-        <v>1.1790281329923273</v>
+        <v>1.4528829469810678</v>
       </c>
       <c r="C3" s="54">
         <f>VLOOKUP(C$1,'FTE Rate Calcs'!$A$2:$B$15,2,FALSE)</f>
-        <v>1.0984236831987697</v>
+        <v>1.2591684358269457</v>
       </c>
       <c r="D3" s="54">
         <f>VLOOKUP(D$1,'FTE Rate Calcs'!$A$2:$B$15,2,FALSE)</f>
-        <v>1.0252202452927968</v>
-      </c>
-      <c r="E3" s="99">
+        <v>1.3199787491847266</v>
+      </c>
+      <c r="E3" s="97">
         <f t="shared" ref="E3:E4" si="1">D3</f>
-        <v>1.0252202452927968</v>
+        <v>1.3199787491847266</v>
       </c>
       <c r="F3" s="54">
         <f>VLOOKUP(F$1,'FTE Rate Calcs'!$A$2:$B$15,2,FALSE)</f>
-        <v>1.0375684282085227</v>
+        <v>1.9089033842911585</v>
       </c>
       <c r="G3" s="54">
         <f>VLOOKUP(G$1,'FTE Rate Calcs'!$A$2:$B$15,2,FALSE)</f>
-        <v>1.0375684282085227</v>
-      </c>
-      <c r="H3" s="99">
+        <v>1.9089033842911585</v>
+      </c>
+      <c r="H3" s="97">
         <f t="shared" ref="H3:H4" si="2">G3</f>
-        <v>1.0375684282085227</v>
+        <v>1.9089033842911585</v>
       </c>
       <c r="I3" s="54">
         <f>VLOOKUP(I$1,'FTE Rate Calcs'!$A$2:$B$15,2,FALSE)</f>
-        <v>1.2081372400182178</v>
+        <v>2.4944485097171891</v>
       </c>
       <c r="J3" s="54">
         <f>VLOOKUP(J$1,'FTE Rate Calcs'!$A$2:$B$15,2,FALSE)</f>
-        <v>1.2081372400182178</v>
+        <v>2.4944485097171891</v>
       </c>
       <c r="K3" s="54">
         <f>VLOOKUP(K$1,'FTE Rate Calcs'!$A$2:$B$15,2,FALSE)</f>
-        <v>1.2081372400182178</v>
-      </c>
-      <c r="L3" s="99">
+        <v>2.4944485097171891</v>
+      </c>
+      <c r="L3" s="97">
         <f t="shared" ref="L3:L4" si="3">K3</f>
-        <v>1.2081372400182178</v>
+        <v>2.4944485097171891</v>
       </c>
       <c r="M3" s="54">
         <f>VLOOKUP(M$1,'FTE Rate Calcs'!$A$2:$B$15,2,FALSE)</f>
-        <v>1.2081372400182178</v>
-      </c>
-      <c r="N3" s="99">
+        <v>2.4944485097171891</v>
+      </c>
+      <c r="N3" s="97">
         <f t="shared" si="0"/>
-        <v>1.2081372400182178</v>
-      </c>
-      <c r="O3" s="99">
+        <v>2.4944485097171891</v>
+      </c>
+      <c r="O3" s="97">
         <f t="shared" si="0"/>
-        <v>1.2081372400182178</v>
-      </c>
-      <c r="P3" s="99">
+        <v>2.4944485097171891</v>
+      </c>
+      <c r="P3" s="97">
         <f t="shared" si="0"/>
-        <v>1.2081372400182178</v>
-      </c>
-      <c r="Q3" s="99">
+        <v>2.4944485097171891</v>
+      </c>
+      <c r="Q3" s="97">
         <f t="shared" si="0"/>
-        <v>1.2081372400182178</v>
-      </c>
-      <c r="R3" s="99">
+        <v>2.4944485097171891</v>
+      </c>
+      <c r="R3" s="97">
         <f t="shared" si="0"/>
-        <v>1.2081372400182178</v>
+        <v>2.4944485097171891</v>
       </c>
       <c r="S3" s="54">
         <f>VLOOKUP(S$1,'FTE Rate Calcs'!$A$2:$B$15,2,FALSE)</f>
-        <v>1.0252202452927968</v>
+        <v>1.1631452329815202</v>
       </c>
       <c r="T3" s="54">
         <f>VLOOKUP(T$1,'FTE Rate Calcs'!$A$2:$B$15,2,FALSE)</f>
-        <v>1.0967771874057404</v>
-      </c>
-      <c r="U3" s="99">
+        <v>1.6817348527651581</v>
+      </c>
+      <c r="U3" s="97">
         <f t="shared" ref="U3:U4" si="4">T3</f>
-        <v>1.0967771874057404</v>
+        <v>1.6817348527651581</v>
       </c>
       <c r="V3" s="54">
         <f>VLOOKUP(V$1,'FTE Rate Calcs'!$A$2:$B$15,2,FALSE)</f>
-        <v>1.0967771874057404</v>
+        <v>1.6817348527651581</v>
       </c>
       <c r="W3" s="54">
         <f>VLOOKUP(W$1,'FTE Rate Calcs'!$A$2:$B$15,2,FALSE)</f>
-        <v>1.0967771874057404</v>
+        <v>1.6817348527651581</v>
       </c>
       <c r="X3" s="54">
         <f>VLOOKUP(X$1,'FTE Rate Calcs'!$A$2:$B$15,2,FALSE)</f>
-        <v>1.0967771874057404</v>
+        <v>1.6817348527651581</v>
       </c>
       <c r="Y3" s="53" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32637,7 +32664,7 @@
         <f>VLOOKUP(D$1,'HBC Rates'!$A$2:$B$15,2,FALSE)</f>
         <v>0.93010000000000004</v>
       </c>
-      <c r="E4" s="99">
+      <c r="E4" s="97">
         <f t="shared" si="1"/>
         <v>0.93010000000000004</v>
       </c>
@@ -32649,7 +32676,7 @@
         <f>VLOOKUP(G$1,'HBC Rates'!$A$2:$B$15,2,FALSE)</f>
         <v>0.67700000000000005</v>
       </c>
-      <c r="H4" s="99">
+      <c r="H4" s="97">
         <f t="shared" si="2"/>
         <v>0.67700000000000005</v>
       </c>
@@ -32665,7 +32692,7 @@
         <f>VLOOKUP(K$1,'HBC Rates'!$A$2:$B$15,2,FALSE)</f>
         <v>0.56869999999999998</v>
       </c>
-      <c r="L4" s="99">
+      <c r="L4" s="97">
         <f t="shared" si="3"/>
         <v>0.56869999999999998</v>
       </c>
@@ -32673,23 +32700,23 @@
         <f>VLOOKUP(M$1,'HBC Rates'!$A$2:$B$15,2,FALSE)</f>
         <v>0.61580000000000001</v>
       </c>
-      <c r="N4" s="99">
+      <c r="N4" s="97">
         <f t="shared" si="0"/>
         <v>0.61580000000000001</v>
       </c>
-      <c r="O4" s="99">
+      <c r="O4" s="97">
         <f t="shared" si="0"/>
         <v>0.61580000000000001</v>
       </c>
-      <c r="P4" s="99">
+      <c r="P4" s="97">
         <f t="shared" si="0"/>
         <v>0.61580000000000001</v>
       </c>
-      <c r="Q4" s="99">
+      <c r="Q4" s="97">
         <f t="shared" si="0"/>
         <v>0.61580000000000001</v>
       </c>
-      <c r="R4" s="99">
+      <c r="R4" s="97">
         <f t="shared" si="0"/>
         <v>0.61580000000000001</v>
       </c>
@@ -32701,7 +32728,7 @@
         <f>VLOOKUP(T$1,'HBC Rates'!$A$2:$B$15,2,FALSE)</f>
         <v>0.94520000000000004</v>
       </c>
-      <c r="U4" s="99">
+      <c r="U4" s="97">
         <f t="shared" si="4"/>
         <v>0.94520000000000004</v>
       </c>
@@ -32718,22 +32745,22 @@
         <v>0.94520000000000004</v>
       </c>
       <c r="Y4" s="53" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A6" s="97" t="s">
+      <c r="A6" s="95" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A7" s="96" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A7" s="98" t="s">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A8" s="96" t="s">
         <v>177</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A8" s="98" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
@@ -32769,31 +32796,31 @@
       <c r="O2" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="P2" s="80" t="str">
+      <c r="P2" s="78" t="str">
         <f>IFERROR((FIND("_",P4)),P4)</f>
         <v>BYU</v>
       </c>
-      <c r="Q2" s="80" t="str">
+      <c r="Q2" s="78" t="str">
         <f>IFERROR((FIND("_",Q4)),Q4)</f>
         <v>ENSIGN</v>
       </c>
-      <c r="R2" s="80" t="str">
+      <c r="R2" s="78" t="str">
         <f>IF(FIND("_",R4),LEFT(R4,FIND("_",R4)-1),R4)</f>
         <v>SLCC</v>
       </c>
-      <c r="S2" s="80" t="str">
+      <c r="S2" s="78" t="str">
         <f>IF(FIND("_",S4),LEFT(S4,FIND("_",S4)-1),S4)</f>
         <v>SLCC</v>
       </c>
-      <c r="T2" s="80" t="str">
+      <c r="T2" s="78" t="str">
         <f>IF(FIND("_",T4),LEFT(T4,FIND("_",T4)-1),T4)</f>
         <v>SLCC</v>
       </c>
-      <c r="U2" s="80" t="str">
+      <c r="U2" s="78" t="str">
         <f>IF(FIND("_",U4),LEFT(U4,FIND("_",U4)-1),U4)</f>
         <v>SLCC</v>
       </c>
-      <c r="V2" s="80" t="str">
+      <c r="V2" s="78" t="str">
         <f>IF(FIND("_",V4),LEFT(V4,FIND("_",V4)-1),V4)</f>
         <v>UOFU</v>
       </c>
@@ -32801,19 +32828,19 @@
       <c r="X2" s="38"/>
       <c r="Y2" s="38"/>
       <c r="Z2" s="38"/>
-      <c r="AA2" s="80" t="str">
+      <c r="AA2" s="78" t="str">
         <f>IF(FIND("_",AA4),LEFT(AA4,FIND("_",AA4)-1),AA4)</f>
         <v>WSU</v>
       </c>
-      <c r="AB2" s="80" t="str">
+      <c r="AB2" s="78" t="str">
         <f>IF(FIND("_",AB4),LEFT(AB4,FIND("_",AB4)-1),AB4)</f>
         <v>WSU</v>
       </c>
-      <c r="AC2" s="80" t="str">
+      <c r="AC2" s="78" t="str">
         <f>IFERROR((FIND("_",AC4)),AC4)</f>
         <v>WESTMIN</v>
       </c>
-      <c r="AD2" s="80"/>
+      <c r="AD2" s="78"/>
     </row>
     <row r="3" spans="15:30" x14ac:dyDescent="0.25">
       <c r="O3" s="7" t="s">
@@ -32825,42 +32852,42 @@
       <c r="Q3" s="35">
         <v>1</v>
       </c>
-      <c r="R3" s="81">
+      <c r="R3" s="79">
         <f>'USHE 2020 Campus Totals'!D3</f>
         <v>0.68409986859395533</v>
       </c>
-      <c r="S3" s="81">
+      <c r="S3" s="79">
         <f>'USHE 2020 Campus Totals'!D6</f>
         <v>0.13337713534822601</v>
       </c>
-      <c r="T3" s="81">
+      <c r="T3" s="79">
         <f>'USHE 2020 Campus Totals'!D7</f>
         <v>1.6162943495400789E-2</v>
       </c>
-      <c r="U3" s="81">
+      <c r="U3" s="79">
         <f>'USHE 2020 Campus Totals'!D10</f>
         <v>0.10175208059570741</v>
       </c>
-      <c r="V3" s="81">
+      <c r="V3" s="79">
         <f>'USHE 2020 Campus Totals'!D19</f>
         <v>0.96822824938358576</v>
       </c>
-      <c r="W3" s="82"/>
-      <c r="X3" s="82"/>
-      <c r="Y3" s="82"/>
-      <c r="Z3" s="82"/>
-      <c r="AA3" s="81">
+      <c r="W3" s="80"/>
+      <c r="X3" s="80"/>
+      <c r="Y3" s="80"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="79">
         <f>'USHE 2020 Campus Totals'!D23</f>
         <v>0.81142857142857139</v>
       </c>
-      <c r="AB3" s="81">
+      <c r="AB3" s="79">
         <f>'USHE 2020 Campus Totals'!D26</f>
         <v>0.16281800391389434</v>
       </c>
       <c r="AC3" s="35">
         <v>1</v>
       </c>
-      <c r="AD3" s="81"/>
+      <c r="AD3" s="79"/>
     </row>
     <row r="4" spans="15:30" x14ac:dyDescent="0.25">
       <c r="O4" s="3" t="s">
@@ -36878,8 +36905,8 @@
       </c>
     </row>
     <row r="66" spans="15:30" x14ac:dyDescent="0.25">
-      <c r="O66" s="105" t="s">
-        <v>197</v>
+      <c r="O66" s="103" t="s">
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -36970,11 +36997,11 @@
         <v>1990</v>
       </c>
       <c r="AJ2" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI2,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI2,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>24311</v>
       </c>
       <c r="AK2" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI2,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI2,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>13449</v>
       </c>
       <c r="AL2" s="37">
@@ -36982,7 +37009,7 @@
         <v>7885</v>
       </c>
       <c r="AM2" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI2,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI2,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>13344</v>
       </c>
       <c r="AN2" s="37">
@@ -37005,11 +37032,11 @@
         <v>1991</v>
       </c>
       <c r="AJ3" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI3,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI3,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>25581</v>
       </c>
       <c r="AK3" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI3,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI3,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>14495</v>
       </c>
       <c r="AL3" s="37">
@@ -37017,7 +37044,7 @@
         <v>8777</v>
       </c>
       <c r="AM3" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI3,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI3,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>15972</v>
       </c>
       <c r="AN3" s="37">
@@ -37040,11 +37067,11 @@
         <v>1992</v>
       </c>
       <c r="AJ4" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI4,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI4,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>25868</v>
       </c>
       <c r="AK4" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI4,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI4,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>14993</v>
       </c>
       <c r="AL4" s="37">
@@ -37052,7 +37079,7 @@
         <v>9623</v>
       </c>
       <c r="AM4" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI4,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI4,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>17766</v>
       </c>
       <c r="AN4" s="37">
@@ -37075,11 +37102,11 @@
         <v>1993</v>
       </c>
       <c r="AJ5" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI5,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI5,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>25982</v>
       </c>
       <c r="AK5" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI5,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI5,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>14447</v>
       </c>
       <c r="AL5" s="37">
@@ -37087,7 +37114,7 @@
         <v>10512</v>
       </c>
       <c r="AM5" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI5,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI5,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>18311</v>
       </c>
       <c r="AN5" s="37">
@@ -37110,11 +37137,11 @@
         <v>1994</v>
       </c>
       <c r="AJ6" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI6,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI6,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>25645</v>
       </c>
       <c r="AK6" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI6,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI6,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>14230</v>
       </c>
       <c r="AL6" s="37">
@@ -37122,7 +37149,7 @@
         <v>13293</v>
       </c>
       <c r="AM6" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI6,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI6,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>19440</v>
       </c>
       <c r="AN6" s="37">
@@ -37145,11 +37172,11 @@
         <v>1995</v>
       </c>
       <c r="AJ7" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI7,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI7,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>26810</v>
       </c>
       <c r="AK7" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI7,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI7,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>13996</v>
       </c>
       <c r="AL7" s="37">
@@ -37157,7 +37184,7 @@
         <v>14040</v>
       </c>
       <c r="AM7" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI7,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI7,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>20834</v>
       </c>
       <c r="AN7" s="37">
@@ -37180,11 +37207,11 @@
         <v>1996</v>
       </c>
       <c r="AJ8" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI8,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI8,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>26079</v>
       </c>
       <c r="AK8" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI8,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI8,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>13906</v>
       </c>
       <c r="AL8" s="37">
@@ -37192,7 +37219,7 @@
         <v>14756</v>
       </c>
       <c r="AM8" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI8,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI8,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>22394</v>
       </c>
       <c r="AN8" s="37">
@@ -37215,11 +37242,11 @@
         <v>1997</v>
       </c>
       <c r="AJ9" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI9,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI9,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>25895</v>
       </c>
       <c r="AK9" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI9,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI9,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>14613</v>
       </c>
       <c r="AL9" s="37">
@@ -37227,7 +37254,7 @@
         <v>15994</v>
       </c>
       <c r="AM9" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI9,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI9,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>24307</v>
       </c>
       <c r="AN9" s="37">
@@ -37250,11 +37277,11 @@
         <v>1998</v>
       </c>
       <c r="AJ10" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI10,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI10,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>25018</v>
       </c>
       <c r="AK10" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI10,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI10,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>13900</v>
       </c>
       <c r="AL10" s="37">
@@ -37262,7 +37289,7 @@
         <v>18174</v>
       </c>
       <c r="AM10" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI10,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI10,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>19754</v>
       </c>
       <c r="AN10" s="37">
@@ -37285,11 +37312,11 @@
         <v>1999</v>
       </c>
       <c r="AJ11" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI11,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI11,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>25781</v>
       </c>
       <c r="AK11" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI11,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI11,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>14984</v>
       </c>
       <c r="AL11" s="37">
@@ -37297,7 +37324,7 @@
         <v>20062</v>
       </c>
       <c r="AM11" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI11,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI11,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>21273</v>
       </c>
       <c r="AN11" s="37">
@@ -37320,11 +37347,11 @@
         <v>2000</v>
       </c>
       <c r="AJ12" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI12,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI12,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>24948</v>
       </c>
       <c r="AK12" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI12,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI12,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>16050</v>
       </c>
       <c r="AL12" s="37">
@@ -37332,7 +37359,7 @@
         <v>20946</v>
       </c>
       <c r="AM12" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI12,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI12,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>21596</v>
       </c>
       <c r="AN12" s="37">
@@ -37355,11 +37382,11 @@
         <v>2001</v>
       </c>
       <c r="AJ13" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI13,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI13,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>27668</v>
       </c>
       <c r="AK13" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI13,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI13,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>16873</v>
       </c>
       <c r="AL13" s="37">
@@ -37367,7 +37394,7 @@
         <v>22609</v>
       </c>
       <c r="AM13" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI13,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI13,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>23701</v>
       </c>
       <c r="AN13" s="37">
@@ -37390,11 +37417,11 @@
         <v>2002</v>
       </c>
       <c r="AJ14" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI14,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI14,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>28369</v>
       </c>
       <c r="AK14" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI14,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI14,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>18059</v>
       </c>
       <c r="AL14" s="37">
@@ -37402,7 +37429,7 @@
         <v>23609</v>
       </c>
       <c r="AM14" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI14,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI14,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>23347</v>
       </c>
       <c r="AN14" s="37">
@@ -37425,11 +37452,11 @@
         <v>2003</v>
       </c>
       <c r="AJ15" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI15,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI15,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>28436</v>
       </c>
       <c r="AK15" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI15,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI15,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>18821</v>
       </c>
       <c r="AL15" s="37">
@@ -37437,7 +37464,7 @@
         <v>23803</v>
       </c>
       <c r="AM15" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI15,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI15,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>24056</v>
       </c>
       <c r="AN15" s="37">
@@ -37462,11 +37489,11 @@
         <v>2004</v>
       </c>
       <c r="AJ16" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI16,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI16,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>28933</v>
       </c>
       <c r="AK16" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI16,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI16,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>18498</v>
       </c>
       <c r="AL16" s="37">
@@ -37474,7 +37501,7 @@
         <v>24149</v>
       </c>
       <c r="AM16" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI16,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI16,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>24725</v>
       </c>
       <c r="AN16" s="37">
@@ -37526,11 +37553,11 @@
         <v>2005</v>
       </c>
       <c r="AJ17" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI17,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI17,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>30558</v>
       </c>
       <c r="AK17" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI17,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI17,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>18142</v>
       </c>
       <c r="AL17" s="37">
@@ -37538,7 +37565,7 @@
         <v>24487</v>
       </c>
       <c r="AM17" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI17,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI17,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>24111</v>
       </c>
       <c r="AN17" s="37">
@@ -37564,11 +37591,11 @@
         <v>2006</v>
       </c>
       <c r="AJ18" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI18,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI18,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>30511</v>
       </c>
       <c r="AK18" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI18,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI18,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>18303</v>
       </c>
       <c r="AL18" s="37">
@@ -37576,7 +37603,7 @@
         <v>23305</v>
       </c>
       <c r="AM18" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI18,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI18,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>24241</v>
       </c>
       <c r="AN18" s="37">
@@ -37605,11 +37632,11 @@
         <v>2007</v>
       </c>
       <c r="AJ19" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI19,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI19,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>28025</v>
       </c>
       <c r="AK19" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI19,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI19,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>18081</v>
       </c>
       <c r="AL19" s="37">
@@ -37617,7 +37644,7 @@
         <v>23840</v>
       </c>
       <c r="AM19" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI19,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI19,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>25235</v>
       </c>
       <c r="AN19" s="37">
@@ -37646,11 +37673,11 @@
         <v>2008</v>
       </c>
       <c r="AJ20" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI20,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI20,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>28211</v>
       </c>
       <c r="AK20" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI20,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI20,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>21388</v>
       </c>
       <c r="AL20" s="37">
@@ -37658,7 +37685,7 @@
         <v>27052</v>
       </c>
       <c r="AM20" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI20,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI20,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>29396</v>
       </c>
       <c r="AN20" s="37">
@@ -37687,11 +37714,11 @@
         <v>2009</v>
       </c>
       <c r="AJ21" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI21,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI21,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>29284</v>
       </c>
       <c r="AK21" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI21,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI21,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>23001</v>
       </c>
       <c r="AL21" s="37">
@@ -37699,7 +37726,7 @@
         <v>29045</v>
       </c>
       <c r="AM21" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI21,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI21,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>34966</v>
       </c>
       <c r="AN21" s="37">
@@ -37728,11 +37755,11 @@
         <v>2010</v>
       </c>
       <c r="AJ22" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI22,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI22,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>30819</v>
       </c>
       <c r="AK22" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI22,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI22,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>24048</v>
       </c>
       <c r="AL22" s="37">
@@ -37740,7 +37767,7 @@
         <v>31739</v>
       </c>
       <c r="AM22" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI22,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI22,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>34654</v>
       </c>
       <c r="AN22" s="37">
@@ -37772,11 +37799,11 @@
         <v>2011</v>
       </c>
       <c r="AJ23" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI23,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI23,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>31660</v>
       </c>
       <c r="AK23" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI23,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI23,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>25301</v>
       </c>
       <c r="AL23" s="37">
@@ -37784,7 +37811,7 @@
         <v>32734</v>
       </c>
       <c r="AM23" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI23,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI23,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>33420</v>
       </c>
       <c r="AN23" s="37">
@@ -37813,11 +37840,11 @@
         <v>2012</v>
       </c>
       <c r="AJ24" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI24,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI24,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>32388</v>
       </c>
       <c r="AK24" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI24,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI24,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>26532</v>
       </c>
       <c r="AL24" s="37">
@@ -37825,7 +37852,7 @@
         <v>31810</v>
       </c>
       <c r="AM24" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI24,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI24,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>29997</v>
       </c>
       <c r="AN24" s="37">
@@ -37853,11 +37880,11 @@
         <v>2013</v>
       </c>
       <c r="AJ25" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI25,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI25,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>32077</v>
       </c>
       <c r="AK25" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI25,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI25,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>25155</v>
       </c>
       <c r="AL25" s="37">
@@ -37865,7 +37892,7 @@
         <v>30880</v>
       </c>
       <c r="AM25" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI25,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI25,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>32003</v>
       </c>
       <c r="AN25" s="37">
@@ -37894,11 +37921,11 @@
         <v>2014</v>
       </c>
       <c r="AJ26" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI26,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI26,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>31515</v>
       </c>
       <c r="AK26" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI26,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI26,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>25954</v>
       </c>
       <c r="AL26" s="37">
@@ -37906,7 +37933,7 @@
         <v>31589</v>
       </c>
       <c r="AM26" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI26,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI26,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>30248</v>
       </c>
       <c r="AN26" s="37">
@@ -37935,11 +37962,11 @@
         <v>2015</v>
       </c>
       <c r="AJ27" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI27,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI27,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>31592</v>
       </c>
       <c r="AK27" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI27,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI27,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>25955</v>
       </c>
       <c r="AL27" s="37">
@@ -37947,7 +37974,7 @@
         <v>33565</v>
       </c>
       <c r="AM27" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI27,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI27,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>29350</v>
       </c>
       <c r="AN27" s="37">
@@ -37976,11 +38003,11 @@
         <v>2016</v>
       </c>
       <c r="AJ28" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI28,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI28,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>31860</v>
       </c>
       <c r="AK28" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI28,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI28,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>26809</v>
       </c>
       <c r="AL28" s="37">
@@ -37988,7 +38015,7 @@
         <v>35126</v>
       </c>
       <c r="AM28" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI28,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI28,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>29901</v>
       </c>
       <c r="AN28" s="37">
@@ -38017,11 +38044,11 @@
         <v>2017</v>
       </c>
       <c r="AJ29" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI29,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI29,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AJ$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>32800</v>
       </c>
       <c r="AK29" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI29,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI29,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AK$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>27949</v>
       </c>
       <c r="AL29" s="37">
@@ -38029,7 +38056,7 @@
         <v>37785</v>
       </c>
       <c r="AM29" s="20">
-        <f>INDEX('Historic from 2019 RTP'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI29,'Historic from 2019 RTP'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic from 2019 RTP'!$B$1:$E$1,0))</f>
+        <f>INDEX('Historic (IPEDS &amp; 2019 RTP)'!$B$2:$E$29,MATCH('College Enrollment Projections'!$AI29,'Historic (IPEDS &amp; 2019 RTP)'!$A$2:$A$29,0),MATCH('College Enrollment Projections'!AM$1,'Historic (IPEDS &amp; 2019 RTP)'!$B$1:$E$1,0))</f>
         <v>29620</v>
       </c>
       <c r="AN29" s="37">
@@ -39279,8 +39306,8 @@
       </c>
     </row>
     <row r="65" spans="35:35" x14ac:dyDescent="0.25">
-      <c r="AI65" s="105" t="s">
-        <v>198</v>
+      <c r="AI65" s="103" t="s">
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -39292,583 +39319,1832 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:T15"/>
+  <dimension ref="A1:AL25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9" style="2"/>
+    <col min="3" max="3" width="10.28515625" style="2" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A1" s="56" t="s">
         <v>48</v>
       </c>
       <c r="B1" s="57" t="s">
-        <v>171</v>
+        <v>170</v>
+      </c>
+      <c r="C1" s="109" t="s">
+        <v>205</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="M1" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="V1" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="W1" s="5"/>
+      <c r="X1" s="5"/>
+    </row>
+    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="77">
-        <f>$E$8</f>
-        <v>1.0252202452927968</v>
+      <c r="B2" s="49">
+        <f>AVERAGE($E$9:$E$23)</f>
+        <v>1.1631452329815202</v>
+      </c>
+      <c r="C2" s="109">
+        <v>1.0249999999999999</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>5</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="I2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="K2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="3" t="s">
         <v>4</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>1</v>
       </c>
       <c r="R2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="S2" s="3" t="s">
+      <c r="T2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="X2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T2" s="3" t="s">
+      <c r="AB2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AF2" s="108" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG2" s="108" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH2" s="108" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="AI2" s="108" t="s">
+        <v>195</v>
+      </c>
+      <c r="AJ2" s="108" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK2" s="108" t="s">
+        <v>2</v>
+      </c>
+      <c r="AL2" s="108" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="76">
-        <f>FTE!$F$3</f>
-        <v>1.1790281329923273</v>
+      <c r="B3" s="49">
+        <f>AVERAGE($F$9:$F$23)</f>
+        <v>1.4528829469810678</v>
+      </c>
+      <c r="C3" s="109">
+        <v>1.179</v>
       </c>
       <c r="D3" s="3">
-        <f>P3</f>
-        <v>2017</v>
-      </c>
-      <c r="E3" s="45">
-        <f>K3/Q3</f>
-        <v>1.0289634146341464</v>
-      </c>
-      <c r="F3" s="45">
-        <f t="shared" ref="F3:F8" si="0">L3/R3</f>
-        <v>1.0375684282085227</v>
-      </c>
-      <c r="G3" s="45">
-        <f t="shared" ref="G3:G8" si="1">M3/S3</f>
-        <v>1.1447347245319457</v>
-      </c>
-      <c r="H3" s="45">
-        <f t="shared" ref="H3:H8" si="2">N3/T3</f>
-        <v>1.0643821742066171</v>
-      </c>
-      <c r="J3" s="3">
-        <v>2017</v>
-      </c>
-      <c r="K3" s="20">
-        <v>33750</v>
-      </c>
-      <c r="L3" s="20">
-        <v>28999</v>
-      </c>
-      <c r="M3" s="20">
-        <v>42678</v>
-      </c>
-      <c r="N3" s="20">
-        <v>31527</v>
-      </c>
-      <c r="P3" s="3">
-        <f t="shared" ref="P3:P10" si="3">J3</f>
-        <v>2017</v>
-      </c>
-      <c r="Q3" s="20">
-        <f>INDEX('USHE Historic'!$B$4:$E$10,MATCH('FTE Rate Calcs'!$P3,'USHE Historic'!$A$4:$A$10,0),MATCH('FTE Rate Calcs'!Q$2,'USHE Historic'!$K$3:$N$3,0))</f>
-        <v>32800</v>
-      </c>
-      <c r="R3" s="20">
-        <f>INDEX('USHE Historic'!$B$4:$E$10,MATCH('FTE Rate Calcs'!$P3,'USHE Historic'!$A$4:$A$10,0),MATCH('FTE Rate Calcs'!R$2,'USHE Historic'!$K$3:$N$3,0))</f>
-        <v>27949</v>
-      </c>
-      <c r="S3" s="20">
-        <f>INDEX('USHE Historic'!$B$4:$E$10,MATCH('FTE Rate Calcs'!$P3,'USHE Historic'!$A$4:$A$10,0),MATCH('FTE Rate Calcs'!S$2,'USHE Historic'!$K$3:$N$3,0))</f>
-        <v>37282</v>
-      </c>
-      <c r="T3" s="20">
-        <f>INDEX('USHE Historic'!$B$4:$E$10,MATCH('FTE Rate Calcs'!$P3,'USHE Historic'!$A$4:$A$10,0),MATCH('FTE Rate Calcs'!T$2,'USHE Historic'!$K$3:$N$3,0))</f>
-        <v>29620</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+        <f t="shared" ref="D3:D23" si="0">V3</f>
+        <v>2002</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="M3" s="3">
+        <v>2002</v>
+      </c>
+      <c r="N3">
+        <v>18280</v>
+      </c>
+      <c r="O3">
+        <v>939</v>
+      </c>
+      <c r="P3">
+        <v>15324</v>
+      </c>
+      <c r="Q3">
+        <v>23687</v>
+      </c>
+      <c r="R3">
+        <v>16755</v>
+      </c>
+      <c r="S3">
+        <v>14003</v>
+      </c>
+      <c r="T3">
+        <v>965</v>
+      </c>
+      <c r="V3" s="3">
+        <v>2002</v>
+      </c>
+      <c r="W3" s="3"/>
+      <c r="X3" s="3"/>
+      <c r="Y3" s="3"/>
+      <c r="Z3" s="3"/>
+      <c r="AA3" s="3"/>
+      <c r="AB3" s="3"/>
+      <c r="AC3" s="3"/>
+    </row>
+    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
         <v>52</v>
       </c>
       <c r="B4" s="49">
-        <f>$H$8</f>
-        <v>1.2081372400182178</v>
+        <f>AVERAGE($G$9:$G$23)</f>
+        <v>2.4944485097171891</v>
+      </c>
+      <c r="C4" s="109">
+        <v>1.208</v>
       </c>
       <c r="D4" s="3">
-        <f t="shared" ref="D4:D10" si="4">P4</f>
-        <v>2018</v>
-      </c>
-      <c r="E4" s="45">
-        <f t="shared" ref="E4:E8" si="5">K4/Q4</f>
-        <v>1.0399418587045393</v>
-      </c>
-      <c r="F4" s="45">
         <f t="shared" si="0"/>
-        <v>1.0505186391475201</v>
-      </c>
-      <c r="G4" s="45">
-        <f t="shared" si="1"/>
-        <v>1.1057073451704189</v>
-      </c>
-      <c r="H4" s="45">
-        <f t="shared" si="2"/>
-        <v>1.0776169570585814</v>
-      </c>
-      <c r="J4" s="3">
-        <v>2018</v>
-      </c>
-      <c r="K4" s="20">
-        <v>34342</v>
-      </c>
-      <c r="L4" s="20">
-        <v>29674</v>
-      </c>
-      <c r="M4" s="20">
-        <v>44152</v>
-      </c>
-      <c r="N4" s="20">
-        <v>31419</v>
-      </c>
-      <c r="P4" s="3">
-        <f t="shared" si="3"/>
-        <v>2018</v>
-      </c>
-      <c r="Q4" s="20">
-        <f>INDEX('USHE Historic'!$B$4:$E$10,MATCH('FTE Rate Calcs'!$P4,'USHE Historic'!$A$4:$A$10,0),MATCH('FTE Rate Calcs'!Q$2,'USHE Historic'!$K$3:$N$3,0))</f>
-        <v>33023</v>
-      </c>
-      <c r="R4" s="20">
-        <f>INDEX('USHE Historic'!$B$4:$E$10,MATCH('FTE Rate Calcs'!$P4,'USHE Historic'!$A$4:$A$10,0),MATCH('FTE Rate Calcs'!R$2,'USHE Historic'!$K$3:$N$3,0))</f>
-        <v>28247</v>
-      </c>
-      <c r="S4" s="20">
-        <f>INDEX('USHE Historic'!$B$4:$E$10,MATCH('FTE Rate Calcs'!$P4,'USHE Historic'!$A$4:$A$10,0),MATCH('FTE Rate Calcs'!S$2,'USHE Historic'!$K$3:$N$3,0))</f>
-        <v>39931</v>
-      </c>
-      <c r="T4" s="20">
-        <f>INDEX('USHE Historic'!$B$4:$E$10,MATCH('FTE Rate Calcs'!$P4,'USHE Historic'!$A$4:$A$10,0),MATCH('FTE Rate Calcs'!T$2,'USHE Historic'!$K$3:$N$3,0))</f>
-        <v>29156</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+        <v>2003</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="M4" s="3">
+        <v>2003</v>
+      </c>
+      <c r="N4">
+        <v>33220</v>
+      </c>
+      <c r="O4">
+        <v>1078</v>
+      </c>
+      <c r="P4">
+        <v>16219</v>
+      </c>
+      <c r="Q4">
+        <v>23549</v>
+      </c>
+      <c r="R4">
+        <v>17986</v>
+      </c>
+      <c r="S4">
+        <v>15369</v>
+      </c>
+      <c r="T4">
+        <v>2087</v>
+      </c>
+      <c r="V4" s="3">
+        <v>2003</v>
+      </c>
+      <c r="W4" s="3"/>
+      <c r="X4" s="3"/>
+      <c r="Y4" s="3"/>
+      <c r="Z4" s="3"/>
+      <c r="AA4" s="3"/>
+      <c r="AB4" s="3"/>
+      <c r="AC4" s="3"/>
+    </row>
+    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>53</v>
       </c>
       <c r="B5" s="49">
-        <f>$H$8</f>
-        <v>1.2081372400182178</v>
+        <f t="shared" ref="B5:B7" si="1">AVERAGE($G$9:$G$23)</f>
+        <v>2.4944485097171891</v>
+      </c>
+      <c r="C5" s="109">
+        <v>1.208</v>
       </c>
       <c r="D5" s="3">
-        <f t="shared" si="4"/>
-        <v>2019</v>
-      </c>
-      <c r="E5" s="45">
-        <f t="shared" si="5"/>
-        <v>1.0652928284427128</v>
-      </c>
-      <c r="F5" s="45">
         <f t="shared" si="0"/>
-        <v>1.0232424773984616</v>
-      </c>
-      <c r="G5" s="45">
-        <f t="shared" si="1"/>
-        <v>1.094756518404908</v>
-      </c>
-      <c r="H5" s="45">
-        <f t="shared" si="2"/>
-        <v>1.0661313819155063</v>
-      </c>
-      <c r="J5" s="3">
-        <v>2019</v>
-      </c>
-      <c r="K5" s="20">
-        <v>34997</v>
-      </c>
-      <c r="L5" s="20">
-        <v>30333</v>
-      </c>
-      <c r="M5" s="20">
-        <v>45682</v>
-      </c>
-      <c r="N5" s="20">
-        <v>31469</v>
-      </c>
-      <c r="P5" s="3">
-        <f t="shared" si="3"/>
-        <v>2019</v>
-      </c>
-      <c r="Q5" s="20">
-        <f>INDEX('USHE Historic'!$B$4:$E$10,MATCH('FTE Rate Calcs'!$P5,'USHE Historic'!$A$4:$A$10,0),MATCH('FTE Rate Calcs'!Q$2,'USHE Historic'!$K$3:$N$3,0))</f>
-        <v>32852</v>
-      </c>
-      <c r="R5" s="20">
-        <f>INDEX('USHE Historic'!$B$4:$E$10,MATCH('FTE Rate Calcs'!$P5,'USHE Historic'!$A$4:$A$10,0),MATCH('FTE Rate Calcs'!R$2,'USHE Historic'!$K$3:$N$3,0))</f>
-        <v>29644</v>
-      </c>
-      <c r="S5" s="20">
-        <f>INDEX('USHE Historic'!$B$4:$E$10,MATCH('FTE Rate Calcs'!$P5,'USHE Historic'!$A$4:$A$10,0),MATCH('FTE Rate Calcs'!S$2,'USHE Historic'!$K$3:$N$3,0))</f>
-        <v>41728</v>
-      </c>
-      <c r="T5" s="20">
-        <f>INDEX('USHE Historic'!$B$4:$E$10,MATCH('FTE Rate Calcs'!$P5,'USHE Historic'!$A$4:$A$10,0),MATCH('FTE Rate Calcs'!T$2,'USHE Historic'!$K$3:$N$3,0))</f>
-        <v>29517</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+        <v>2004</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="M5" s="3">
+        <v>2004</v>
+      </c>
+      <c r="N5">
+        <v>33495</v>
+      </c>
+      <c r="O5">
+        <v>1141</v>
+      </c>
+      <c r="P5">
+        <v>16571</v>
+      </c>
+      <c r="Q5">
+        <v>25736</v>
+      </c>
+      <c r="R5">
+        <v>17713</v>
+      </c>
+      <c r="S5">
+        <v>15886</v>
+      </c>
+      <c r="T5">
+        <v>2223</v>
+      </c>
+      <c r="V5" s="3">
+        <v>2004</v>
+      </c>
+      <c r="W5" s="3"/>
+      <c r="X5" s="3"/>
+      <c r="Y5" s="3"/>
+      <c r="Z5" s="3"/>
+      <c r="AA5" s="3"/>
+      <c r="AB5" s="3"/>
+      <c r="AC5" s="3"/>
+    </row>
+    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
         <v>54</v>
       </c>
       <c r="B6" s="49">
-        <f>$H$8</f>
-        <v>1.2081372400182178</v>
+        <f t="shared" si="1"/>
+        <v>2.4944485097171891</v>
+      </c>
+      <c r="C6" s="109">
+        <v>1.208</v>
       </c>
       <c r="D6" s="3">
-        <f t="shared" si="4"/>
-        <v>2020</v>
-      </c>
-      <c r="E6" s="45">
-        <f t="shared" si="5"/>
-        <v>1.0764812575574365</v>
-      </c>
-      <c r="F6" s="45">
         <f t="shared" si="0"/>
-        <v>1.0475402081362346</v>
-      </c>
-      <c r="G6" s="45">
-        <f t="shared" si="1"/>
-        <v>1.1547293335939026</v>
-      </c>
-      <c r="H6" s="45">
-        <f t="shared" si="2"/>
-        <v>1.166306378924999</v>
-      </c>
-      <c r="J6" s="3">
-        <v>2020</v>
-      </c>
-      <c r="K6" s="20">
-        <v>35610</v>
-      </c>
-      <c r="L6" s="20">
-        <v>31003</v>
-      </c>
-      <c r="M6" s="20">
-        <v>47270</v>
-      </c>
-      <c r="N6" s="20">
-        <v>31832</v>
-      </c>
-      <c r="P6" s="3">
-        <f t="shared" si="3"/>
-        <v>2020</v>
-      </c>
-      <c r="Q6" s="20">
-        <f>INDEX('USHE Historic'!$B$4:$E$10,MATCH('FTE Rate Calcs'!$P6,'USHE Historic'!$A$4:$A$10,0),MATCH('FTE Rate Calcs'!Q$2,'USHE Historic'!$K$3:$N$3,0))</f>
-        <v>33080</v>
-      </c>
-      <c r="R6" s="20">
-        <f>INDEX('USHE Historic'!$B$4:$E$10,MATCH('FTE Rate Calcs'!$P6,'USHE Historic'!$A$4:$A$10,0),MATCH('FTE Rate Calcs'!R$2,'USHE Historic'!$K$3:$N$3,0))</f>
-        <v>29596</v>
-      </c>
-      <c r="S6" s="20">
-        <f>INDEX('USHE Historic'!$B$4:$E$10,MATCH('FTE Rate Calcs'!$P6,'USHE Historic'!$A$4:$A$10,0),MATCH('FTE Rate Calcs'!S$2,'USHE Historic'!$K$3:$N$3,0))</f>
-        <v>40936</v>
-      </c>
-      <c r="T6" s="20">
-        <f>INDEX('USHE Historic'!$B$4:$E$10,MATCH('FTE Rate Calcs'!$P6,'USHE Historic'!$A$4:$A$10,0),MATCH('FTE Rate Calcs'!T$2,'USHE Historic'!$K$3:$N$3,0))</f>
-        <v>27293</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+        <v>2005</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="M6" s="3">
+        <v>2005</v>
+      </c>
+      <c r="N6">
+        <v>36473</v>
+      </c>
+      <c r="O6">
+        <v>1158</v>
+      </c>
+      <c r="P6">
+        <v>16701</v>
+      </c>
+      <c r="Q6">
+        <v>25801</v>
+      </c>
+      <c r="R6">
+        <v>17112</v>
+      </c>
+      <c r="S6">
+        <v>15562</v>
+      </c>
+      <c r="T6">
+        <v>2167</v>
+      </c>
+      <c r="V6" s="3">
+        <v>2005</v>
+      </c>
+      <c r="W6" s="3"/>
+      <c r="X6" s="3"/>
+      <c r="Y6" s="3"/>
+      <c r="Z6" s="3"/>
+      <c r="AA6" s="3"/>
+      <c r="AB6" s="3"/>
+      <c r="AC6" s="3"/>
+    </row>
+    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
         <v>55</v>
       </c>
       <c r="B7" s="49">
-        <f>$H$8</f>
-        <v>1.2081372400182178</v>
+        <f t="shared" si="1"/>
+        <v>2.4944485097171891</v>
+      </c>
+      <c r="C7" s="109">
+        <v>1.208</v>
       </c>
       <c r="D7" s="3">
-        <f t="shared" si="4"/>
-        <v>2021</v>
-      </c>
-      <c r="E7" s="45">
-        <f t="shared" si="5"/>
-        <v>1.0333120538564216</v>
-      </c>
-      <c r="F7" s="45">
         <f t="shared" si="0"/>
-        <v>1.0412776247732922</v>
-      </c>
-      <c r="G7" s="45">
-        <f t="shared" si="1"/>
-        <v>1.145606126702535</v>
-      </c>
-      <c r="H7" s="45">
-        <f t="shared" si="2"/>
-        <v>1.1692194674012857</v>
-      </c>
-      <c r="J7" s="3">
-        <v>2021</v>
-      </c>
-      <c r="K7" s="20">
-        <v>35610</v>
-      </c>
-      <c r="L7" s="20">
-        <v>31003</v>
-      </c>
-      <c r="M7" s="20">
-        <v>47270</v>
-      </c>
-      <c r="N7" s="20">
-        <v>31832</v>
-      </c>
-      <c r="P7" s="3">
-        <f t="shared" si="3"/>
-        <v>2021</v>
-      </c>
-      <c r="Q7" s="20">
-        <f>INDEX('USHE Historic'!$B$4:$E$10,MATCH('FTE Rate Calcs'!$P7,'USHE Historic'!$A$4:$A$10,0),MATCH('FTE Rate Calcs'!Q$2,'USHE Historic'!$K$3:$N$3,0))</f>
-        <v>34462</v>
-      </c>
-      <c r="R7" s="20">
-        <f>INDEX('USHE Historic'!$B$4:$E$10,MATCH('FTE Rate Calcs'!$P7,'USHE Historic'!$A$4:$A$10,0),MATCH('FTE Rate Calcs'!R$2,'USHE Historic'!$K$3:$N$3,0))</f>
-        <v>29774</v>
-      </c>
-      <c r="S7" s="20">
-        <f>INDEX('USHE Historic'!$B$4:$E$10,MATCH('FTE Rate Calcs'!$P7,'USHE Historic'!$A$4:$A$10,0),MATCH('FTE Rate Calcs'!S$2,'USHE Historic'!$K$3:$N$3,0))</f>
-        <v>41262</v>
-      </c>
-      <c r="T7" s="20">
-        <f>INDEX('USHE Historic'!$B$4:$E$10,MATCH('FTE Rate Calcs'!$P7,'USHE Historic'!$A$4:$A$10,0),MATCH('FTE Rate Calcs'!T$2,'USHE Historic'!$K$3:$N$3,0))</f>
-        <v>27225</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+        <v>2006</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="M7" s="3">
+        <v>2006</v>
+      </c>
+      <c r="N7">
+        <v>32725</v>
+      </c>
+      <c r="O7">
+        <v>1153</v>
+      </c>
+      <c r="P7">
+        <v>15819</v>
+      </c>
+      <c r="Q7">
+        <v>25968</v>
+      </c>
+      <c r="R7">
+        <v>16508</v>
+      </c>
+      <c r="S7">
+        <v>14318</v>
+      </c>
+      <c r="T7">
+        <v>2111</v>
+      </c>
+      <c r="V7" s="3">
+        <v>2006</v>
+      </c>
+      <c r="W7" s="3"/>
+      <c r="X7" s="3"/>
+      <c r="Y7" s="3"/>
+      <c r="Z7" s="3"/>
+      <c r="AA7" s="3"/>
+      <c r="AB7" s="3"/>
+      <c r="AC7" s="3"/>
+    </row>
+    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>100</v>
       </c>
       <c r="B8" s="49">
-        <f>$E$8</f>
-        <v>1.0252202452927968</v>
+        <f>AVERAGE($H$9:$H$23)</f>
+        <v>1.3199787491847266</v>
+      </c>
+      <c r="C8" s="109">
+        <v>1.0249999999999999</v>
       </c>
       <c r="D8" s="3">
-        <f t="shared" si="4"/>
-        <v>2022</v>
-      </c>
-      <c r="E8" s="58">
-        <f t="shared" si="5"/>
-        <v>1.0252202452927968</v>
-      </c>
-      <c r="F8" s="58">
         <f t="shared" si="0"/>
-        <v>1.0364043591629337</v>
-      </c>
-      <c r="G8" s="58">
-        <f t="shared" si="1"/>
-        <v>1.0967771874057404</v>
-      </c>
-      <c r="H8" s="58">
-        <f t="shared" si="2"/>
-        <v>1.2081372400182178</v>
-      </c>
-      <c r="J8" s="3">
-        <v>2022</v>
-      </c>
-      <c r="K8" s="20">
-        <v>35610</v>
-      </c>
-      <c r="L8" s="20">
-        <v>31003</v>
-      </c>
-      <c r="M8" s="20">
-        <v>47270</v>
-      </c>
-      <c r="N8" s="20">
-        <v>31832</v>
-      </c>
-      <c r="P8" s="3">
-        <f t="shared" si="3"/>
-        <v>2022</v>
-      </c>
-      <c r="Q8" s="20">
-        <f>INDEX('USHE Historic'!$B$4:$E$10,MATCH('FTE Rate Calcs'!$P8,'USHE Historic'!$A$4:$A$10,0),MATCH('FTE Rate Calcs'!Q$2,'USHE Historic'!$K$3:$N$3,0))</f>
-        <v>34734</v>
-      </c>
-      <c r="R8" s="20">
-        <f>INDEX('USHE Historic'!$B$4:$E$10,MATCH('FTE Rate Calcs'!$P8,'USHE Historic'!$A$4:$A$10,0),MATCH('FTE Rate Calcs'!R$2,'USHE Historic'!$K$3:$N$3,0))</f>
-        <v>29914</v>
-      </c>
-      <c r="S8" s="20">
-        <f>INDEX('USHE Historic'!$B$4:$E$10,MATCH('FTE Rate Calcs'!$P8,'USHE Historic'!$A$4:$A$10,0),MATCH('FTE Rate Calcs'!S$2,'USHE Historic'!$K$3:$N$3,0))</f>
-        <v>43099</v>
-      </c>
-      <c r="T8" s="20">
-        <f>INDEX('USHE Historic'!$B$4:$E$10,MATCH('FTE Rate Calcs'!$P8,'USHE Historic'!$A$4:$A$10,0),MATCH('FTE Rate Calcs'!T$2,'USHE Historic'!$K$3:$N$3,0))</f>
-        <v>26348</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+        <v>2007</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="M8" s="3">
+        <v>2007</v>
+      </c>
+      <c r="N8">
+        <v>32811</v>
+      </c>
+      <c r="O8">
+        <v>1307</v>
+      </c>
+      <c r="P8">
+        <v>15830</v>
+      </c>
+      <c r="Q8">
+        <v>25784</v>
+      </c>
+      <c r="R8">
+        <v>16572</v>
+      </c>
+      <c r="S8">
+        <v>18972</v>
+      </c>
+      <c r="T8">
+        <v>2223</v>
+      </c>
+      <c r="V8" s="3">
+        <v>2007</v>
+      </c>
+      <c r="W8" s="3"/>
+      <c r="X8" s="3"/>
+      <c r="Y8" s="3"/>
+      <c r="Z8" s="3"/>
+      <c r="AA8" s="3"/>
+      <c r="AB8" s="3"/>
+      <c r="AC8" s="3"/>
+    </row>
+    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>101</v>
       </c>
       <c r="B9" s="49">
-        <f>$G$8</f>
-        <v>1.0967771874057404</v>
+        <f>AVERAGE($I$9:$I$23)</f>
+        <v>1.6817348527651581</v>
+      </c>
+      <c r="C9" s="109">
+        <v>1.097</v>
       </c>
       <c r="D9" s="3">
-        <f t="shared" si="4"/>
-        <v>2023</v>
-      </c>
-      <c r="E9" s="45"/>
-      <c r="F9" s="45"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="45"/>
-      <c r="J9" s="3">
-        <v>2023</v>
-      </c>
-      <c r="K9" s="20"/>
-      <c r="L9" s="20"/>
-      <c r="M9" s="20"/>
-      <c r="N9" s="20"/>
-      <c r="P9" s="3">
-        <f t="shared" si="3"/>
-        <v>2023</v>
-      </c>
-      <c r="Q9" s="20"/>
-      <c r="R9" s="20"/>
-      <c r="S9" s="20"/>
-      <c r="T9" s="20"/>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>2008</v>
+      </c>
+      <c r="E9" s="45">
+        <f>W9/N9</f>
+        <v>1.1376363270121723</v>
+      </c>
+      <c r="F9" s="45">
+        <f t="shared" ref="F9:K9" si="2">X9/O9</f>
+        <v>1.3876755070202809</v>
+      </c>
+      <c r="G9" s="45">
+        <f t="shared" si="2"/>
+        <v>2.9850249584026622</v>
+      </c>
+      <c r="H9" s="45">
+        <f t="shared" si="2"/>
+        <v>1.384923495954498</v>
+      </c>
+      <c r="I9" s="45">
+        <f t="shared" si="2"/>
+        <v>1.7918011992619927</v>
+      </c>
+      <c r="J9" s="45">
+        <f t="shared" si="2"/>
+        <v>1.4993340343498072</v>
+      </c>
+      <c r="K9" s="45">
+        <f t="shared" si="2"/>
+        <v>1.24947501049979</v>
+      </c>
+      <c r="M9" s="3">
+        <v>2008</v>
+      </c>
+      <c r="N9">
+        <v>34751</v>
+      </c>
+      <c r="O9">
+        <v>1282</v>
+      </c>
+      <c r="P9">
+        <v>15626</v>
+      </c>
+      <c r="Q9">
+        <v>24966</v>
+      </c>
+      <c r="R9">
+        <v>17344</v>
+      </c>
+      <c r="S9">
+        <v>14265</v>
+      </c>
+      <c r="T9">
+        <v>2381</v>
+      </c>
+      <c r="V9" s="3">
+        <v>2008</v>
+      </c>
+      <c r="W9">
+        <v>39534</v>
+      </c>
+      <c r="X9">
+        <v>1779</v>
+      </c>
+      <c r="Y9">
+        <v>46644</v>
+      </c>
+      <c r="Z9">
+        <v>34576</v>
+      </c>
+      <c r="AA9">
+        <v>31077</v>
+      </c>
+      <c r="AB9">
+        <v>21388</v>
+      </c>
+      <c r="AC9">
+        <v>2975</v>
+      </c>
+    </row>
+    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>121</v>
       </c>
       <c r="B10" s="49">
-        <f>$G$8</f>
-        <v>1.0967771874057404</v>
+        <f t="shared" ref="B10:B12" si="3">AVERAGE($I$9:$I$23)</f>
+        <v>1.6817348527651581</v>
+      </c>
+      <c r="C10" s="109">
+        <v>1.097</v>
       </c>
       <c r="D10" s="3">
-        <f t="shared" si="4"/>
-        <v>2024</v>
-      </c>
-      <c r="E10" s="45"/>
-      <c r="F10" s="45"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="45"/>
-      <c r="J10" s="3">
-        <v>2024</v>
-      </c>
-      <c r="K10" s="20"/>
-      <c r="L10" s="20"/>
-      <c r="M10" s="20"/>
-      <c r="N10" s="20"/>
-      <c r="P10" s="3">
-        <f t="shared" si="3"/>
-        <v>2024</v>
-      </c>
-      <c r="Q10" s="20"/>
-      <c r="R10" s="20"/>
-      <c r="S10" s="20"/>
-      <c r="T10" s="20"/>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>2009</v>
+      </c>
+      <c r="E10" s="45">
+        <f t="shared" ref="E10:E22" si="4">W10/N10</f>
+        <v>1.2265873129417151</v>
+      </c>
+      <c r="F10" s="45">
+        <f t="shared" ref="F10:F23" si="5">X10/O10</f>
+        <v>1.2588797814207651</v>
+      </c>
+      <c r="G10" s="45">
+        <f t="shared" ref="G10:G23" si="6">Y10/P10</f>
+        <v>2.8967671498756595</v>
+      </c>
+      <c r="H10" s="45">
+        <f t="shared" ref="H10:H23" si="7">Z10/Q10</f>
+        <v>1.3564526855220436</v>
+      </c>
+      <c r="I10" s="45">
+        <f t="shared" ref="I10:I23" si="8">AA10/R10</f>
+        <v>1.7775990034774485</v>
+      </c>
+      <c r="J10" s="45">
+        <f t="shared" ref="J10:J23" si="9">AB10/S10</f>
+        <v>1.9136675964351317</v>
+      </c>
+      <c r="K10" s="45">
+        <f t="shared" ref="K10:K23" si="10">AC10/T10</f>
+        <v>1.2381329113924051</v>
+      </c>
+      <c r="M10" s="3">
+        <v>2009</v>
+      </c>
+      <c r="N10">
+        <v>34949</v>
+      </c>
+      <c r="O10">
+        <v>1464</v>
+      </c>
+      <c r="P10">
+        <v>16487</v>
+      </c>
+      <c r="Q10">
+        <v>25563</v>
+      </c>
+      <c r="R10">
+        <v>19267</v>
+      </c>
+      <c r="S10">
+        <v>14699</v>
+      </c>
+      <c r="T10">
+        <v>2528</v>
+      </c>
+      <c r="V10" s="3">
+        <v>2009</v>
+      </c>
+      <c r="W10">
+        <v>42868</v>
+      </c>
+      <c r="X10">
+        <v>1843</v>
+      </c>
+      <c r="Y10">
+        <v>47759</v>
+      </c>
+      <c r="Z10">
+        <v>34675</v>
+      </c>
+      <c r="AA10">
+        <v>34249</v>
+      </c>
+      <c r="AB10">
+        <v>28129</v>
+      </c>
+      <c r="AC10">
+        <v>3130</v>
+      </c>
+    </row>
+    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>122</v>
       </c>
       <c r="B11" s="49">
-        <f>$G$8</f>
-        <v>1.0967771874057404</v>
-      </c>
-      <c r="K11" s="42" t="s">
-        <v>195</v>
-      </c>
-      <c r="Q11" s="42" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v>1.6817348527651581</v>
+      </c>
+      <c r="C11" s="109">
+        <v>1.097</v>
+      </c>
+      <c r="D11" s="3">
+        <f t="shared" si="0"/>
+        <v>2010</v>
+      </c>
+      <c r="E11" s="45">
+        <f t="shared" si="4"/>
+        <v>1.1242677943823756</v>
+      </c>
+      <c r="F11" s="45">
+        <f t="shared" si="5"/>
+        <v>1.3232077764277035</v>
+      </c>
+      <c r="G11" s="45">
+        <f t="shared" si="6"/>
+        <v>2.657093653446791</v>
+      </c>
+      <c r="H11" s="45">
+        <f t="shared" si="7"/>
+        <v>1.3293523025084237</v>
+      </c>
+      <c r="I11" s="45">
+        <f t="shared" si="8"/>
+        <v>1.7051044083526683</v>
+      </c>
+      <c r="J11" s="45">
+        <f t="shared" si="9"/>
+        <v>1.9291648447748142</v>
+      </c>
+      <c r="K11" s="45">
+        <f t="shared" si="10"/>
+        <v>1.3535727508330249</v>
+      </c>
+      <c r="M11" s="3">
+        <v>2010</v>
+      </c>
+      <c r="N11">
+        <v>34997</v>
+      </c>
+      <c r="O11">
+        <v>1646</v>
+      </c>
+      <c r="P11">
+        <v>19743</v>
+      </c>
+      <c r="Q11">
+        <v>26710</v>
+      </c>
+      <c r="R11">
+        <v>21550</v>
+      </c>
+      <c r="S11">
+        <v>16009</v>
+      </c>
+      <c r="T11">
+        <v>2701</v>
+      </c>
+      <c r="V11" s="3">
+        <v>2010</v>
+      </c>
+      <c r="W11">
+        <v>39346</v>
+      </c>
+      <c r="X11">
+        <v>2178</v>
+      </c>
+      <c r="Y11">
+        <v>52459</v>
+      </c>
+      <c r="Z11">
+        <v>35507</v>
+      </c>
+      <c r="AA11">
+        <v>36745</v>
+      </c>
+      <c r="AB11">
+        <v>30884</v>
+      </c>
+      <c r="AC11">
+        <v>3656</v>
+      </c>
+    </row>
+    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>123</v>
       </c>
       <c r="B12" s="49">
-        <f>$G$8</f>
-        <v>1.0967771874057404</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v>1.6817348527651581</v>
+      </c>
+      <c r="C12" s="109">
+        <v>1.097</v>
+      </c>
+      <c r="D12" s="3">
+        <f t="shared" si="0"/>
+        <v>2011</v>
+      </c>
+      <c r="E12" s="45">
+        <f t="shared" si="4"/>
+        <v>1.1498069498069499</v>
+      </c>
+      <c r="F12" s="45">
+        <f t="shared" si="5"/>
+        <v>1.3630326508024351</v>
+      </c>
+      <c r="G12" s="45">
+        <f t="shared" si="6"/>
+        <v>2.2779327096077724</v>
+      </c>
+      <c r="H12" s="45">
+        <f t="shared" si="7"/>
+        <v>1.3121524457195481</v>
+      </c>
+      <c r="I12" s="45">
+        <f t="shared" si="8"/>
+        <v>1.7044436068182771</v>
+      </c>
+      <c r="J12" s="45">
+        <f t="shared" si="9"/>
+        <v>1.8614504042013336</v>
+      </c>
+      <c r="K12" s="45">
+        <f t="shared" si="10"/>
+        <v>1.3406862745098038</v>
+      </c>
+      <c r="M12" s="3">
+        <v>2011</v>
+      </c>
+      <c r="N12">
+        <v>34965</v>
+      </c>
+      <c r="O12">
+        <v>1807</v>
+      </c>
+      <c r="P12">
+        <v>22232</v>
+      </c>
+      <c r="Q12">
+        <v>28233</v>
+      </c>
+      <c r="R12">
+        <v>23877</v>
+      </c>
+      <c r="S12">
+        <v>16947</v>
+      </c>
+      <c r="T12">
+        <v>2856</v>
+      </c>
+      <c r="V12" s="3">
+        <v>2011</v>
+      </c>
+      <c r="W12">
+        <v>40203</v>
+      </c>
+      <c r="X12">
+        <v>2463</v>
+      </c>
+      <c r="Y12">
+        <v>50643</v>
+      </c>
+      <c r="Z12">
+        <v>37046</v>
+      </c>
+      <c r="AA12">
+        <v>40697</v>
+      </c>
+      <c r="AB12">
+        <v>31546</v>
+      </c>
+      <c r="AC12">
+        <v>3829</v>
+      </c>
+    </row>
+    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
         <v>107</v>
       </c>
       <c r="B13" s="49">
-        <f>$F$3</f>
-        <v>1.0375684282085227</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+        <f>AVERAGE($J$9:$J$23)</f>
+        <v>1.9089033842911585</v>
+      </c>
+      <c r="C13" s="109">
+        <v>1.038</v>
+      </c>
+      <c r="D13" s="3">
+        <f t="shared" si="0"/>
+        <v>2012</v>
+      </c>
+      <c r="E13" s="45">
+        <f t="shared" si="4"/>
+        <v>1.1541191747222623</v>
+      </c>
+      <c r="F13" s="45">
+        <f t="shared" si="5"/>
+        <v>1.3779443254817987</v>
+      </c>
+      <c r="G13" s="45">
+        <f t="shared" si="6"/>
+        <v>2.259221595636498</v>
+      </c>
+      <c r="H13" s="45">
+        <f t="shared" si="7"/>
+        <v>1.4064457747459278</v>
+      </c>
+      <c r="I13" s="45">
+        <f t="shared" si="8"/>
+        <v>1.701041028781384</v>
+      </c>
+      <c r="J13" s="45">
+        <f t="shared" si="9"/>
+        <v>1.8549458033028772</v>
+      </c>
+      <c r="K13" s="45">
+        <f t="shared" si="10"/>
+        <v>1.37029501525941</v>
+      </c>
+      <c r="M13" s="3">
+        <v>2012</v>
+      </c>
+      <c r="N13">
+        <v>34655</v>
+      </c>
+      <c r="O13">
+        <v>1868</v>
+      </c>
+      <c r="P13">
+        <v>21634</v>
+      </c>
+      <c r="Q13">
+        <v>28732</v>
+      </c>
+      <c r="R13">
+        <v>24495</v>
+      </c>
+      <c r="S13">
+        <v>17621</v>
+      </c>
+      <c r="T13">
+        <v>2949</v>
+      </c>
+      <c r="V13" s="3">
+        <v>2012</v>
+      </c>
+      <c r="W13">
+        <v>39996</v>
+      </c>
+      <c r="X13">
+        <v>2574</v>
+      </c>
+      <c r="Y13">
+        <v>48876</v>
+      </c>
+      <c r="Z13">
+        <v>40410</v>
+      </c>
+      <c r="AA13">
+        <v>41667</v>
+      </c>
+      <c r="AB13">
+        <v>32686</v>
+      </c>
+      <c r="AC13">
+        <v>4041</v>
+      </c>
+    </row>
+    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>106</v>
       </c>
       <c r="B14" s="49">
-        <f>$F$3</f>
-        <v>1.0375684282085227</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+        <f>AVERAGE($J$9:$J$23)</f>
+        <v>1.9089033842911585</v>
+      </c>
+      <c r="C14" s="109">
+        <v>1.038</v>
+      </c>
+      <c r="D14" s="3">
+        <f t="shared" si="0"/>
+        <v>2014</v>
+      </c>
+      <c r="E14" s="45">
+        <f t="shared" si="4"/>
+        <v>1.2232998295421149</v>
+      </c>
+      <c r="F14" s="45">
+        <f t="shared" si="5"/>
+        <v>1.4089363768819816</v>
+      </c>
+      <c r="G14" s="45">
+        <f t="shared" si="6"/>
+        <v>2.2887435687839592</v>
+      </c>
+      <c r="H14" s="45">
+        <f t="shared" si="7"/>
+        <v>1.3151234777876046</v>
+      </c>
+      <c r="I14" s="45">
+        <f t="shared" si="8"/>
+        <v>1.6703787103377687</v>
+      </c>
+      <c r="J14" s="45">
+        <f t="shared" si="9"/>
+        <v>1.9287242427654543</v>
+      </c>
+      <c r="K14" s="45">
+        <f t="shared" si="10"/>
+        <v>1.3306620209059234</v>
+      </c>
+      <c r="M14" s="3">
+        <v>2014</v>
+      </c>
+      <c r="N14">
+        <v>34026</v>
+      </c>
+      <c r="O14">
+        <v>2059</v>
+      </c>
+      <c r="P14">
+        <v>20797</v>
+      </c>
+      <c r="Q14">
+        <v>29398</v>
+      </c>
+      <c r="R14">
+        <v>24425</v>
+      </c>
+      <c r="S14">
+        <v>17762</v>
+      </c>
+      <c r="T14">
+        <v>2870</v>
+      </c>
+      <c r="V14" s="3">
+        <v>2014</v>
+      </c>
+      <c r="W14">
+        <v>41624</v>
+      </c>
+      <c r="X14">
+        <v>2901</v>
+      </c>
+      <c r="Y14">
+        <v>47599</v>
+      </c>
+      <c r="Z14">
+        <v>38662</v>
+      </c>
+      <c r="AA14">
+        <v>40799</v>
+      </c>
+      <c r="AB14">
+        <v>34258</v>
+      </c>
+      <c r="AC14">
+        <v>3819</v>
+      </c>
+    </row>
+    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="76">
-        <f>FTE!F7</f>
-        <v>1.0984236831987697</v>
-      </c>
+      <c r="B15" s="49">
+        <f>AVERAGE($K$9:$K$23)</f>
+        <v>1.2591684358269457</v>
+      </c>
+      <c r="C15" s="109">
+        <v>1.0980000000000001</v>
+      </c>
+      <c r="D15" s="3">
+        <f t="shared" si="0"/>
+        <v>2015</v>
+      </c>
+      <c r="E15" s="45">
+        <f t="shared" si="4"/>
+        <v>1.1808754643837829</v>
+      </c>
+      <c r="F15" s="45">
+        <f t="shared" si="5"/>
+        <v>1.4359110169491525</v>
+      </c>
+      <c r="G15" s="45">
+        <f t="shared" si="6"/>
+        <v>2.3420302893987106</v>
+      </c>
+      <c r="H15" s="45">
+        <f t="shared" si="7"/>
+        <v>1.3020822506322973</v>
+      </c>
+      <c r="I15" s="45">
+        <f t="shared" si="8"/>
+        <v>1.6799642750818695</v>
+      </c>
+      <c r="J15" s="45">
+        <f t="shared" si="9"/>
+        <v>1.9344583754233764</v>
+      </c>
+      <c r="K15" s="45">
+        <f t="shared" si="10"/>
+        <v>1.2941176470588236</v>
+      </c>
+      <c r="M15" s="3">
+        <v>2015</v>
+      </c>
+      <c r="N15">
+        <v>30955</v>
+      </c>
+      <c r="O15">
+        <v>1888</v>
+      </c>
+      <c r="P15">
+        <v>20007</v>
+      </c>
+      <c r="Q15">
+        <v>28863</v>
+      </c>
+      <c r="R15">
+        <v>23513</v>
+      </c>
+      <c r="S15">
+        <v>16829</v>
+      </c>
+      <c r="T15">
+        <v>2754</v>
+      </c>
+      <c r="V15" s="3">
+        <v>2015</v>
+      </c>
+      <c r="W15">
+        <v>36554</v>
+      </c>
+      <c r="X15">
+        <v>2711</v>
+      </c>
+      <c r="Y15">
+        <v>46857</v>
+      </c>
+      <c r="Z15">
+        <v>37582</v>
+      </c>
+      <c r="AA15">
+        <v>39501</v>
+      </c>
+      <c r="AB15">
+        <v>32555</v>
+      </c>
+      <c r="AC15">
+        <v>3564</v>
+      </c>
+    </row>
+    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="D16" s="3">
+        <f t="shared" si="0"/>
+        <v>2016</v>
+      </c>
+      <c r="E16" s="45">
+        <f t="shared" si="4"/>
+        <v>1.2050937049495436</v>
+      </c>
+      <c r="F16" s="45">
+        <f t="shared" si="5"/>
+        <v>1.4893062076160668</v>
+      </c>
+      <c r="G16" s="45">
+        <f t="shared" si="6"/>
+        <v>2.4036828698790065</v>
+      </c>
+      <c r="H16" s="45">
+        <f t="shared" si="7"/>
+        <v>1.2783430732210381</v>
+      </c>
+      <c r="I16" s="45">
+        <f t="shared" si="8"/>
+        <v>1.589301692277767</v>
+      </c>
+      <c r="J16" s="45">
+        <f t="shared" si="9"/>
+        <v>1.967741935483871</v>
+      </c>
+      <c r="K16" s="45">
+        <f t="shared" si="10"/>
+        <v>1.3047404063205417</v>
+      </c>
+      <c r="M16" s="3">
+        <v>2016</v>
+      </c>
+      <c r="N16">
+        <v>31215</v>
+      </c>
+      <c r="O16">
+        <v>1917</v>
+      </c>
+      <c r="P16">
+        <v>18844</v>
+      </c>
+      <c r="Q16">
+        <v>29090</v>
+      </c>
+      <c r="R16">
+        <v>25705</v>
+      </c>
+      <c r="S16">
+        <v>16988</v>
+      </c>
+      <c r="T16">
+        <v>2658</v>
+      </c>
+      <c r="V16" s="3">
+        <v>2016</v>
+      </c>
+      <c r="W16">
+        <v>37617</v>
+      </c>
+      <c r="X16">
+        <v>2855</v>
+      </c>
+      <c r="Y16">
+        <v>45295</v>
+      </c>
+      <c r="Z16">
+        <v>37187</v>
+      </c>
+      <c r="AA16">
+        <v>40853</v>
+      </c>
+      <c r="AB16">
+        <v>33428</v>
+      </c>
+      <c r="AC16">
+        <v>3468</v>
+      </c>
+    </row>
+    <row r="17" spans="4:29" x14ac:dyDescent="0.25">
+      <c r="D17" s="3">
+        <f t="shared" si="0"/>
+        <v>2017</v>
+      </c>
+      <c r="E17" s="45">
+        <f t="shared" si="4"/>
+        <v>1.1748100213725956</v>
+      </c>
+      <c r="F17" s="45">
+        <f t="shared" si="5"/>
+        <v>1.4544568923526546</v>
+      </c>
+      <c r="G17" s="45">
+        <f t="shared" si="6"/>
+        <v>2.4315789473684211</v>
+      </c>
+      <c r="H17" s="45">
+        <f t="shared" si="7"/>
+        <v>1.3045120745657393</v>
+      </c>
+      <c r="I17" s="45">
+        <f t="shared" si="8"/>
+        <v>1.6871351856175578</v>
+      </c>
+      <c r="J17" s="45">
+        <f t="shared" si="9"/>
+        <v>1.9193812983360674</v>
+      </c>
+      <c r="K17" s="45">
+        <f t="shared" si="10"/>
+        <v>1.2417168674698795</v>
+      </c>
+      <c r="M17" s="3">
+        <v>2017</v>
+      </c>
+      <c r="N17">
+        <v>33688</v>
+      </c>
+      <c r="O17">
+        <v>2053</v>
+      </c>
+      <c r="P17">
+        <v>17765</v>
+      </c>
+      <c r="Q17">
+        <v>28324</v>
+      </c>
+      <c r="R17">
+        <v>25698</v>
+      </c>
+      <c r="S17">
+        <v>17068</v>
+      </c>
+      <c r="T17">
+        <v>2656</v>
+      </c>
+      <c r="V17" s="3">
+        <f>M17</f>
+        <v>2017</v>
+      </c>
+      <c r="W17">
+        <v>39577</v>
+      </c>
+      <c r="X17">
+        <v>2986</v>
+      </c>
+      <c r="Y17">
+        <v>43197</v>
+      </c>
+      <c r="Z17">
+        <v>36949</v>
+      </c>
+      <c r="AA17">
+        <v>43356</v>
+      </c>
+      <c r="AB17">
+        <v>32760</v>
+      </c>
+      <c r="AC17">
+        <v>3298</v>
+      </c>
+    </row>
+    <row r="18" spans="4:29" x14ac:dyDescent="0.25">
+      <c r="D18" s="3">
+        <f t="shared" si="0"/>
+        <v>2018</v>
+      </c>
+      <c r="E18" s="45">
+        <f t="shared" si="4"/>
+        <v>1.1425684842536732</v>
+      </c>
+      <c r="F18" s="45">
+        <f t="shared" si="5"/>
+        <v>1.4874569601574028</v>
+      </c>
+      <c r="G18" s="45">
+        <f t="shared" si="6"/>
+        <v>2.463401821153397</v>
+      </c>
+      <c r="H18" s="45">
+        <f t="shared" si="7"/>
+        <v>1.3176623194502874</v>
+      </c>
+      <c r="I18" s="45">
+        <f t="shared" si="8"/>
+        <v>1.6994498708880657</v>
+      </c>
+      <c r="J18" s="45">
+        <f t="shared" si="9"/>
+        <v>1.9365125464684014</v>
+      </c>
+      <c r="K18" s="45">
+        <f t="shared" si="10"/>
+        <v>1.2380576391630478</v>
+      </c>
+      <c r="M18" s="3">
+        <v>2018</v>
+      </c>
+      <c r="N18">
+        <v>34643</v>
+      </c>
+      <c r="O18">
+        <v>2033</v>
+      </c>
+      <c r="P18">
+        <v>17132</v>
+      </c>
+      <c r="Q18">
+        <v>28524</v>
+      </c>
+      <c r="R18">
+        <v>26721</v>
+      </c>
+      <c r="S18">
+        <v>17216</v>
+      </c>
+      <c r="T18">
+        <v>2533</v>
+      </c>
+      <c r="V18" s="3">
+        <f>M18</f>
+        <v>2018</v>
+      </c>
+      <c r="W18">
+        <v>39582</v>
+      </c>
+      <c r="X18">
+        <v>3024</v>
+      </c>
+      <c r="Y18">
+        <v>42203</v>
+      </c>
+      <c r="Z18">
+        <v>37585</v>
+      </c>
+      <c r="AA18">
+        <v>45411</v>
+      </c>
+      <c r="AB18">
+        <v>33339</v>
+      </c>
+      <c r="AC18">
+        <v>3136</v>
+      </c>
+    </row>
+    <row r="19" spans="4:29" x14ac:dyDescent="0.25">
+      <c r="D19" s="3">
+        <f t="shared" si="0"/>
+        <v>2019</v>
+      </c>
+      <c r="E19" s="45">
+        <f t="shared" si="4"/>
+        <v>1.159103575723798</v>
+      </c>
+      <c r="F19" s="45">
+        <f t="shared" si="5"/>
+        <v>1.4476334340382679</v>
+      </c>
+      <c r="G19" s="45">
+        <f t="shared" si="6"/>
+        <v>2.4449628477622256</v>
+      </c>
+      <c r="H19" s="45">
+        <f t="shared" si="7"/>
+        <v>1.3190601062728591</v>
+      </c>
+      <c r="I19" s="45">
+        <f t="shared" si="8"/>
+        <v>1.7257189173949816</v>
+      </c>
+      <c r="J19" s="45">
+        <f t="shared" si="9"/>
+        <v>1.983936866849499</v>
+      </c>
+      <c r="K19" s="45">
+        <f t="shared" si="10"/>
+        <v>1.1908027430415491</v>
+      </c>
+      <c r="M19" s="3">
+        <v>2019</v>
+      </c>
+      <c r="N19">
+        <v>34091</v>
+      </c>
+      <c r="O19">
+        <v>1986</v>
+      </c>
+      <c r="P19">
+        <v>17361</v>
+      </c>
+      <c r="Q19">
+        <v>28982</v>
+      </c>
+      <c r="R19">
+        <v>28376</v>
+      </c>
+      <c r="S19">
+        <v>17867</v>
+      </c>
+      <c r="T19">
+        <v>2479</v>
+      </c>
+      <c r="V19" s="3">
+        <f>M19</f>
+        <v>2019</v>
+      </c>
+      <c r="W19">
+        <v>39515</v>
+      </c>
+      <c r="X19">
+        <v>2875</v>
+      </c>
+      <c r="Y19">
+        <v>42447</v>
+      </c>
+      <c r="Z19">
+        <v>38229</v>
+      </c>
+      <c r="AA19">
+        <v>48969</v>
+      </c>
+      <c r="AB19">
+        <v>35447</v>
+      </c>
+      <c r="AC19">
+        <v>2952</v>
+      </c>
+    </row>
+    <row r="20" spans="4:29" x14ac:dyDescent="0.25">
+      <c r="D20" s="3">
+        <f t="shared" si="0"/>
+        <v>2020</v>
+      </c>
+      <c r="E20" s="45">
+        <f t="shared" si="4"/>
+        <v>1.1570425858204554</v>
+      </c>
+      <c r="F20" s="45">
+        <f t="shared" si="5"/>
+        <v>1.4526315789473685</v>
+      </c>
+      <c r="G20" s="45">
+        <f t="shared" si="6"/>
+        <v>2.4458427770487892</v>
+      </c>
+      <c r="H20" s="45">
+        <f t="shared" si="7"/>
+        <v>1.3113930922168691</v>
+      </c>
+      <c r="I20" s="45">
+        <f t="shared" si="8"/>
+        <v>1.5093581544848831</v>
+      </c>
+      <c r="J20" s="45">
+        <f t="shared" si="9"/>
+        <v>1.9747424939732632</v>
+      </c>
+      <c r="K20" s="45">
+        <f t="shared" si="10"/>
+        <v>1.1743892165122156</v>
+      </c>
+      <c r="M20" s="3">
+        <v>2020</v>
+      </c>
+      <c r="N20">
+        <v>33908</v>
+      </c>
+      <c r="O20">
+        <v>1900</v>
+      </c>
+      <c r="P20">
+        <v>16766</v>
+      </c>
+      <c r="Q20">
+        <v>29474</v>
+      </c>
+      <c r="R20">
+        <v>29867</v>
+      </c>
+      <c r="S20">
+        <v>18252</v>
+      </c>
+      <c r="T20">
+        <v>2374</v>
+      </c>
+      <c r="V20" s="3">
+        <f>M20</f>
+        <v>2020</v>
+      </c>
+      <c r="W20">
+        <v>39233</v>
+      </c>
+      <c r="X20">
+        <v>2760</v>
+      </c>
+      <c r="Y20">
+        <v>41007</v>
+      </c>
+      <c r="Z20">
+        <v>38652</v>
+      </c>
+      <c r="AA20">
+        <v>45080</v>
+      </c>
+      <c r="AB20">
+        <v>36043</v>
+      </c>
+      <c r="AC20">
+        <v>2788</v>
+      </c>
+    </row>
+    <row r="21" spans="4:29" x14ac:dyDescent="0.25">
+      <c r="D21" s="3">
+        <f t="shared" si="0"/>
+        <v>2021</v>
+      </c>
+      <c r="E21" s="45">
+        <f t="shared" si="4"/>
+        <v>1.1181485295800435</v>
+      </c>
+      <c r="F21" s="45">
+        <f t="shared" si="5"/>
+        <v>1.4377142857142857</v>
+      </c>
+      <c r="G21" s="45">
+        <f t="shared" si="6"/>
+        <v>2.4956873475700436</v>
+      </c>
+      <c r="H21" s="45">
+        <f t="shared" si="7"/>
+        <v>1.2787284432436039</v>
+      </c>
+      <c r="I21" s="45">
+        <f t="shared" si="8"/>
+        <v>1.5841580695925861</v>
+      </c>
+      <c r="J21" s="45">
+        <f t="shared" si="9"/>
+        <v>1.9782058871011139</v>
+      </c>
+      <c r="K21" s="45">
+        <f t="shared" si="10"/>
+        <v>1.133552014995314</v>
+      </c>
+      <c r="M21" s="3">
+        <v>2021</v>
+      </c>
+      <c r="N21">
+        <v>34956</v>
+      </c>
+      <c r="O21">
+        <v>1750</v>
+      </c>
+      <c r="P21">
+        <v>16811</v>
+      </c>
+      <c r="Q21">
+        <v>29979</v>
+      </c>
+      <c r="R21">
+        <v>28595</v>
+      </c>
+      <c r="S21">
+        <v>18583</v>
+      </c>
+      <c r="T21">
+        <v>2134</v>
+      </c>
+      <c r="V21" s="3">
+        <f>M21</f>
+        <v>2021</v>
+      </c>
+      <c r="W21">
+        <v>39086</v>
+      </c>
+      <c r="X21">
+        <v>2516</v>
+      </c>
+      <c r="Y21">
+        <v>41955</v>
+      </c>
+      <c r="Z21">
+        <v>38335</v>
+      </c>
+      <c r="AA21">
+        <v>45299</v>
+      </c>
+      <c r="AB21">
+        <v>36761</v>
+      </c>
+      <c r="AC21">
+        <v>2419</v>
+      </c>
+    </row>
+    <row r="22" spans="4:29" x14ac:dyDescent="0.25">
+      <c r="D22" s="3">
+        <f t="shared" si="0"/>
+        <v>2022</v>
+      </c>
+      <c r="E22" s="45">
+        <f t="shared" si="4"/>
+        <v>1.1385080306676367</v>
+      </c>
+      <c r="F22" s="45">
+        <f t="shared" si="5"/>
+        <v>1.4944512946979038</v>
+      </c>
+      <c r="G22" s="45">
+        <f t="shared" si="6"/>
+        <v>2.4698267775623788</v>
+      </c>
+      <c r="H22" s="45">
+        <f t="shared" si="7"/>
+        <v>1.299531145344943</v>
+      </c>
+      <c r="I22" s="45">
+        <f t="shared" si="8"/>
+        <v>1.5820706614110585</v>
+      </c>
+      <c r="J22" s="45">
+        <f t="shared" si="9"/>
+        <v>1.9558494187906581</v>
+      </c>
+      <c r="K22" s="45">
+        <f t="shared" si="10"/>
+        <v>1.2335115864527628</v>
+      </c>
+      <c r="M22" s="3">
+        <v>2022</v>
+      </c>
+      <c r="N22">
+        <v>35738</v>
+      </c>
+      <c r="O22">
+        <v>1622</v>
+      </c>
+      <c r="P22">
+        <v>15991</v>
+      </c>
+      <c r="Q22">
+        <v>29860</v>
+      </c>
+      <c r="R22">
+        <v>27653</v>
+      </c>
+      <c r="S22">
+        <v>18754</v>
+      </c>
+      <c r="T22">
+        <v>1683</v>
+      </c>
+      <c r="V22" s="3">
+        <f>M22</f>
+        <v>2022</v>
+      </c>
+      <c r="W22">
+        <v>40688</v>
+      </c>
+      <c r="X22">
+        <v>2424</v>
+      </c>
+      <c r="Y22">
+        <v>39495</v>
+      </c>
+      <c r="Z22">
+        <v>38804</v>
+      </c>
+      <c r="AA22">
+        <v>43749</v>
+      </c>
+      <c r="AB22">
+        <v>36680</v>
+      </c>
+      <c r="AC22">
+        <v>2076</v>
+      </c>
+    </row>
+    <row r="23" spans="4:29" x14ac:dyDescent="0.25">
+      <c r="D23" s="3">
+        <f t="shared" si="0"/>
+        <v>2023</v>
+      </c>
+      <c r="E23" s="58">
+        <f>W23/N23</f>
+        <v>1.1553107095636845</v>
+      </c>
+      <c r="F23" s="58">
+        <f t="shared" si="5"/>
+        <v>1.974006116207951</v>
+      </c>
+      <c r="G23" s="58">
+        <f t="shared" si="6"/>
+        <v>2.554930332261522</v>
+      </c>
+      <c r="H23" s="58">
+        <f t="shared" si="7"/>
+        <v>1.2839185505852173</v>
+      </c>
+      <c r="I23" s="58">
+        <f t="shared" si="8"/>
+        <v>1.8184980076990613</v>
+      </c>
+      <c r="J23" s="58">
+        <f t="shared" si="9"/>
+        <v>1.9954350161117078</v>
+      </c>
+      <c r="K23" s="58">
+        <f t="shared" si="10"/>
+        <v>1.1938144329896907</v>
+      </c>
+      <c r="M23" s="3">
+        <v>2023</v>
+      </c>
+      <c r="N23">
+        <v>34035</v>
+      </c>
+      <c r="O23">
+        <v>2616</v>
+      </c>
+      <c r="P23">
+        <v>14928</v>
+      </c>
+      <c r="Q23">
+        <v>31185</v>
+      </c>
+      <c r="R23">
+        <v>29614</v>
+      </c>
+      <c r="S23">
+        <v>18620</v>
+      </c>
+      <c r="T23">
+        <v>1455</v>
+      </c>
+      <c r="V23" s="3">
+        <f>M23</f>
+        <v>2023</v>
+      </c>
+      <c r="W23">
+        <v>39321</v>
+      </c>
+      <c r="X23">
+        <v>5164</v>
+      </c>
+      <c r="Y23">
+        <v>38140</v>
+      </c>
+      <c r="Z23">
+        <v>40039</v>
+      </c>
+      <c r="AA23">
+        <v>53853</v>
+      </c>
+      <c r="AB23">
+        <v>37155</v>
+      </c>
+      <c r="AC23">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="24" spans="4:29" x14ac:dyDescent="0.25">
+      <c r="D24" s="3">
+        <f t="shared" ref="D18:D24" si="11">V24</f>
+        <v>2024</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="M24" s="3">
+        <v>2024</v>
+      </c>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
+      <c r="S24" s="3"/>
+      <c r="T24" s="3"/>
+      <c r="V24" s="3">
+        <f>M24</f>
+        <v>2024</v>
+      </c>
+      <c r="W24" s="3"/>
+      <c r="X24" s="3"/>
+      <c r="Y24" s="3"/>
+      <c r="Z24" s="3"/>
+      <c r="AA24" s="3"/>
+      <c r="AB24" s="3"/>
+      <c r="AC24" s="3"/>
+    </row>
+    <row r="25" spans="4:29" x14ac:dyDescent="0.25">
+      <c r="Q25" s="42"/>
+      <c r="Z25" s="42"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -39885,7 +41161,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.85546875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" style="2" customWidth="1"/>
     <col min="3" max="3" width="9" style="2"/>
     <col min="4" max="4" width="20.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.5703125" style="2" bestFit="1" customWidth="1"/>
@@ -39896,7 +41172,7 @@
     <col min="10" max="10" width="12" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.42578125" style="2" customWidth="1"/>
     <col min="14" max="14" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="8.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="11.140625" style="2" bestFit="1" customWidth="1"/>
@@ -39921,35 +41197,35 @@
         <v>48</v>
       </c>
       <c r="B1" s="57" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D1" s="39"/>
       <c r="E1" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="F1" s="76" t="s">
         <v>149</v>
       </c>
-      <c r="F1" s="78" t="s">
+      <c r="G1" s="76" t="s">
         <v>150</v>
       </c>
-      <c r="G1" s="78" t="s">
+      <c r="H1" s="76" t="s">
         <v>151</v>
       </c>
-      <c r="H1" s="78" t="s">
+      <c r="I1" s="39" t="s">
         <v>152</v>
       </c>
-      <c r="I1" s="39" t="s">
-        <v>153</v>
-      </c>
-      <c r="J1" s="78" t="s">
+      <c r="J1" s="76" t="s">
         <v>108</v>
       </c>
       <c r="K1" s="39" t="s">
         <v>106</v>
       </c>
       <c r="L1" s="39" t="s">
+        <v>153</v>
+      </c>
+      <c r="M1" s="76" t="s">
         <v>154</v>
-      </c>
-      <c r="M1" s="78" t="s">
-        <v>155</v>
       </c>
       <c r="N1" s="39" t="s">
         <v>55</v>
@@ -39958,46 +41234,46 @@
         <v>53</v>
       </c>
       <c r="P1" s="39" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q1" s="39" t="s">
         <v>54</v>
       </c>
       <c r="R1" s="39" t="s">
+        <v>156</v>
+      </c>
+      <c r="S1" s="39" t="s">
         <v>157</v>
       </c>
-      <c r="S1" s="39" t="s">
+      <c r="T1" s="39" t="s">
         <v>158</v>
       </c>
-      <c r="T1" s="39" t="s">
+      <c r="U1" s="39" t="s">
         <v>159</v>
       </c>
-      <c r="U1" s="39" t="s">
+      <c r="V1" s="39" t="s">
         <v>160</v>
       </c>
-      <c r="V1" s="39" t="s">
+      <c r="W1" s="76" t="s">
+        <v>15</v>
+      </c>
+      <c r="X1" s="76" t="s">
         <v>161</v>
       </c>
-      <c r="W1" s="78" t="s">
-        <v>15</v>
-      </c>
-      <c r="X1" s="78" t="s">
+      <c r="Y1" s="39" t="s">
         <v>162</v>
       </c>
-      <c r="Y1" s="39" t="s">
+      <c r="Z1" s="39" t="s">
         <v>163</v>
       </c>
-      <c r="Z1" s="39" t="s">
+      <c r="AA1" s="39" t="s">
         <v>164</v>
       </c>
-      <c r="AA1" s="39" t="s">
+      <c r="AB1" s="39" t="s">
         <v>165</v>
       </c>
-      <c r="AB1" s="39" t="s">
+      <c r="AC1" s="39" t="s">
         <v>166</v>
-      </c>
-      <c r="AC1" s="39" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.25">
@@ -40005,11 +41281,11 @@
         <v>15</v>
       </c>
       <c r="B2" s="49">
-        <f>$W$2</f>
+        <f>_xlfn.XLOOKUP($A2,$D$1:$AC$1,$D$2:$AC$2)</f>
         <v>0.93010000000000004</v>
       </c>
-      <c r="D2" s="79" t="s">
-        <v>170</v>
+      <c r="D2" s="77" t="s">
+        <v>169</v>
       </c>
       <c r="E2" s="39">
         <v>3</v>
@@ -40096,7 +41372,7 @@
         <v>0.94520000000000004</v>
       </c>
       <c r="AC2" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.25">
@@ -40108,7 +41384,7 @@
         <v>0.93010000000000004</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.25">
@@ -40119,8 +41395,8 @@
         <f>$M$2</f>
         <v>0.62190000000000001</v>
       </c>
-      <c r="D4" s="104" t="s">
-        <v>194</v>
+      <c r="D4" s="102" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.25">
@@ -40239,7 +41515,11 @@
     <col min="2" max="2" width="10.7109375" style="2" customWidth="1"/>
     <col min="3" max="5" width="9" style="2"/>
     <col min="6" max="6" width="10.42578125" style="7" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="2"/>
+    <col min="7" max="7" width="9" style="2"/>
+    <col min="8" max="8" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="16" width="9" style="2"/>
+    <col min="17" max="17" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
@@ -40252,7 +41532,7 @@
       <c r="E1" s="62"/>
       <c r="F1" s="63"/>
       <c r="G1" s="5" t="s">
-        <v>148</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="30.75" x14ac:dyDescent="0.3">
@@ -40263,20 +41543,18 @@
         <v>50</v>
       </c>
       <c r="C2" s="65" t="s">
+        <v>125</v>
+      </c>
+      <c r="D2" s="66" t="s">
+        <v>171</v>
+      </c>
+      <c r="E2" s="66" t="s">
+        <v>172</v>
+      </c>
+      <c r="F2" s="67" t="s">
         <v>126</v>
       </c>
-      <c r="D2" s="66" t="s">
-        <v>172</v>
-      </c>
-      <c r="E2" s="66" t="s">
-        <v>173</v>
-      </c>
-      <c r="F2" s="67" t="s">
-        <v>127</v>
-      </c>
-      <c r="G2" s="42" t="s">
-        <v>193</v>
-      </c>
+      <c r="G2" s="42"/>
     </row>
     <row r="3" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="68">
@@ -40325,13 +41603,13 @@
         <v>50</v>
       </c>
       <c r="C6" s="65" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D6" s="66" t="s">
+        <v>171</v>
+      </c>
+      <c r="E6" s="66" t="s">
         <v>172</v>
-      </c>
-      <c r="E6" s="66" t="s">
-        <v>173</v>
       </c>
       <c r="F6" s="63"/>
     </row>
@@ -40392,18 +41670,18 @@
         <v>48</v>
       </c>
       <c r="B1" s="57" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D1" s="21"/>
       <c r="E1" s="21"/>
       <c r="F1" s="21"/>
       <c r="G1" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H1" s="21"/>
       <c r="I1" s="21"/>
       <c r="J1" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -40434,19 +41712,19 @@
         <v>0.10050000000000003</v>
       </c>
       <c r="D3" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="E3" s="21" t="s">
         <v>129</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>130</v>
       </c>
       <c r="F3" s="21" t="s">
         <v>48</v>
       </c>
       <c r="G3" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="H3" s="21" t="s">
         <v>131</v>
-      </c>
-      <c r="H3" s="21" t="s">
-        <v>132</v>
       </c>
       <c r="I3" s="21"/>
     </row>
@@ -40462,10 +41740,10 @@
         <v>2.0099999999999998</v>
       </c>
       <c r="E4" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="F4" s="21" t="s">
         <v>133</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>134</v>
       </c>
       <c r="G4" s="22">
         <v>8082</v>
@@ -40485,7 +41763,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F5" s="21"/>
       <c r="G5" s="22">
@@ -40509,10 +41787,10 @@
       </c>
       <c r="D6" s="21"/>
       <c r="E6" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="F6" s="21" t="s">
         <v>136</v>
-      </c>
-      <c r="F6" s="21" t="s">
-        <v>137</v>
       </c>
       <c r="G6" s="22">
         <v>25265</v>
@@ -40537,10 +41815,10 @@
         <v>6.01</v>
       </c>
       <c r="E7" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="F7" s="21" t="s">
         <v>138</v>
-      </c>
-      <c r="F7" s="21" t="s">
-        <v>139</v>
       </c>
       <c r="G7" s="22">
         <v>16472</v>
@@ -40560,10 +41838,10 @@
         <v>7.01</v>
       </c>
       <c r="E8" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="F8" s="21" t="s">
         <v>140</v>
-      </c>
-      <c r="F8" s="21" t="s">
-        <v>141</v>
       </c>
       <c r="G8" s="22">
         <v>23172</v>
@@ -40588,7 +41866,7 @@
         <v>8</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F9" s="21"/>
       <c r="G9" s="22">
@@ -40614,10 +41892,10 @@
         <v>9.01</v>
       </c>
       <c r="E10" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="F10" s="21" t="s">
         <v>143</v>
-      </c>
-      <c r="F10" s="21" t="s">
-        <v>144</v>
       </c>
       <c r="G10" s="22">
         <v>15191</v>
@@ -40642,10 +41920,10 @@
         <v>9.02</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G11" s="22">
         <v>3557</v>
@@ -40670,7 +41948,7 @@
         <v>10</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F12" s="21"/>
       <c r="G12" s="22">
@@ -40693,7 +41971,7 @@
         <v>0.21501653575857793</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E13" s="21"/>
       <c r="F13" s="21"/>
@@ -40933,13 +42211,13 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="102">
+      <c r="A13" s="100">
         <v>46006</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
